--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-15T19:11:07+00:00</t>
+    <t>2026-01-16T14:21:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-16T14:21:16+00:00</t>
+    <t>2026-01-19T10:22:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T10:22:08+00:00</t>
+    <t>2026-01-20T10:13:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T10:13:19+00:00</t>
+    <t>2026-01-21T17:03:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T17:03:29+00:00</t>
+    <t>2026-01-22T09:24:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-22T09:24:15+00:00</t>
+    <t>2026-01-22T12:59:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-22T12:59:21+00:00</t>
+    <t>2026-01-22T14:02:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -9,11 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$30</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1068" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1066" uniqueCount="282">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-22T14:02:02+00:00</t>
+    <t>2026-01-23T19:34:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t xml:space="preserve">**Beschreibung:** Bildet den Medikationsplan eines ELGA Teilnehmers ab. Enthält verordnete Arzneimittel und deren Dosierung in Form von 0..* Medikationsplaneinträgen (AtEmedMedicationRequestPlaneintrag). </t>
+    <t>**Beschreibung:** Bildet den Medikationsplan eines ELGA Teilnehmers ab. Enthält verordnete Arzneimittel und deren Dosierung in Form von 0..* Medikationsplaneinträgen (AtEmedMedicationRequestPlaneintrag). Die Reihenfolge der Einträge ist fachlich relevant.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -464,7 +467,7 @@
 </t>
   </si>
   <si>
-    <t>Business identifier</t>
+    <t>Eindeutige Kennung der Liste. Keine Verwendung in der Liste für den Medikationsplan.</t>
   </si>
   <si>
     <t>Identifier for the List assigned for business purposes outside the context of FHIR.</t>
@@ -479,7 +482,7 @@
     <t>List.status</t>
   </si>
   <si>
-    <t>current | retired | entered-in-error</t>
+    <t>Der Medikationsplan ist aktuell: current | retired | entered-in-error. https://hl7.org/fhir/R4/valueset-list-status.html</t>
   </si>
   <si>
     <t>Indicates the current state of this list.</t>
@@ -488,6 +491,9 @@
     <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
   </si>
   <si>
+    <t>current</t>
+  </si>
+  <si>
     <t>required</t>
   </si>
   <si>
@@ -506,7 +512,7 @@
     <t>List.mode</t>
   </si>
   <si>
-    <t>working | snapshot | changes</t>
+    <t>Der Medikationsplan ist ein Arbeitsdokument: working | snapshot | changes. https://hl7.org/fhir/R4/valueset-list-mode.html</t>
   </si>
   <si>
     <t>How this list was prepared - whether it is a working list that is suitable for being maintained on an ongoing basis, or if it represents a snapshot of a list of items from another source, or whether it is a prepared list where items may be marked as added, modified or deleted.</t>
@@ -516,6 +522,9 @@
   </si>
   <si>
     <t>Lists are used in various ways, and it must be known in what way it is safe to use them.</t>
+  </si>
+  <si>
+    <t>working</t>
   </si>
   <si>
     <t>The processing mode that applies to this list.</t>
@@ -559,7 +568,7 @@
 </t>
   </si>
   <si>
-    <t>What the purpose of this list is</t>
+    <t>Code, der den Typ der Liste beschreibt. https://hl7.org/fhir/R4/valueset-list-example-codes.html. Zu prüfen, ob/wie in Medikationsplan verwendet.</t>
   </si>
   <si>
     <t>This code defines the purpose of the list - why it was created.</t>
@@ -593,7 +602,7 @@
 </t>
   </si>
   <si>
-    <t>If all resources have the same subject</t>
+    <t>Keine Verwendung in der Liste für den Medikationsplan.</t>
   </si>
   <si>
     <t>The common subject (or patient) of the resources that are in the list if there is one.</t>
@@ -618,9 +627,6 @@
 </t>
   </si>
   <si>
-    <t>Context in which list created</t>
-  </si>
-  <si>
     <t>The encounter that is the context in which this list was created.</t>
   </si>
   <si>
@@ -637,7 +643,7 @@
 </t>
   </si>
   <si>
-    <t>When the list was prepared</t>
+    <t>Letzte Aktualisierung der Liste des Medikationsplans.</t>
   </si>
   <si>
     <t>The date that the list was prepared.</t>
@@ -666,7 +672,7 @@
 </t>
   </si>
   <si>
-    <t>Who and/or what defined the list contents (aka Author)</t>
+    <t>Ersteller der Liste des Medikationsplans.</t>
   </si>
   <si>
     <t>The entity responsible for deciding what the contents of the list were. Where the list was created by a human, this is the same as the author of the list.</t>
@@ -687,7 +693,7 @@
     <t>List.orderedBy</t>
   </si>
   <si>
-    <t>What order the list has</t>
+    <t>Die Reihenfolge der Einträge im Medikationsplan ist fachlich relevant und wird durch den Ersteller der Liste vorgegeben. Mögliche Codes: user | system | event-date | entry-date| priority | alphabetic | category | patient.</t>
   </si>
   <si>
     <t>What order applies to the items in the list.</t>
@@ -699,10 +705,14 @@
     <t>Important for presentation and rendering.  Lists may be sorted to place more important information first or to group related entries.</t>
   </si>
   <si>
-    <t>What order applies to the items in a list.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/list-order|4.0.1</t>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;code value="user"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/list-order</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=COMP].sequenceNumber &gt; 1</t>
@@ -791,7 +801,7 @@
     <t>List.entry.flag</t>
   </si>
   <si>
-    <t>Status/Workflow information about this item</t>
+    <t>Kennzeichnet die Art der Änderung des Medikationsplaneintrags</t>
   </si>
   <si>
     <t>The flag allows the system constructing the list to indicate the role and significance of the item in the list.</t>
@@ -803,10 +813,7 @@
     <t>This field is present to support various clinical uses of lists, such as a discharge summary medication list, where flags specify whether the medication was added, modified, or deleted from the list.</t>
   </si>
   <si>
-    <t>Codes that provide further information about the reason and meaning of the item in the list.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/list-item-flag|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/list-item-flag</t>
   </si>
   <si>
     <t>List.entry.deleted</t>
@@ -816,7 +823,7 @@
 </t>
   </si>
   <si>
-    <t>If this item is actually marked as deleted</t>
+    <t>Gibt an, ob der referenzierte Medikationsplaneintrag aus dem Medikationsplan entfernt wurde.</t>
   </si>
   <si>
     <t>True if this item is marked as deleted in the list.</t>
@@ -856,11 +863,11 @@
     <t>List.entry.item</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-medicationrequest-planeintrag)
 </t>
   </si>
   <si>
-    <t>Actual entry</t>
+    <t>Referenz auf einen Medikationsplaneintrag.</t>
   </si>
   <si>
     <t>A reference to the actual resource from which data was derived.</t>
@@ -872,7 +879,7 @@
     <t>List.emptyReason</t>
   </si>
   <si>
-    <t>Why list is empty</t>
+    <t>Grund, warum die Liste keine Einträge enthält. Zu prüfen, ob/wie in Liste des Medikationsplan verwendet.</t>
   </si>
   <si>
     <t>If the list is empty, why the list is empty.</t>
@@ -1019,6 +1026,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1213,7 +1235,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="62.41796875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="82.0390625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1227,7 +1249,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="73.66015625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="36.34375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="41.86328125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -1358,7 +1380,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>31</v>
       </c>
@@ -1464,7 +1486,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>84</v>
       </c>
@@ -1572,7 +1594,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>92</v>
       </c>
@@ -1678,7 +1700,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>98</v>
       </c>
@@ -1786,7 +1808,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>104</v>
       </c>
@@ -1894,7 +1916,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>113</v>
       </c>
@@ -2002,7 +2024,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>121</v>
       </c>
@@ -2110,7 +2132,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>129</v>
       </c>
@@ -2218,7 +2240,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>137</v>
       </c>
@@ -2328,7 +2350,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>142</v>
       </c>
@@ -2453,7 +2475,7 @@
         <v>85</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>86</v>
@@ -2482,7 +2504,7 @@
         <v>21</v>
       </c>
       <c r="S12" t="s" s="2">
-        <v>21</v>
+        <v>152</v>
       </c>
       <c r="T12" t="s" s="2">
         <v>21</v>
@@ -2497,13 +2519,13 @@
         <v>21</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>21</v>
@@ -2536,18 +2558,18 @@
         <v>97</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2561,7 +2583,7 @@
         <v>85</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>86</v>
@@ -2573,16 +2595,16 @@
         <v>105</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>21</v>
@@ -2592,7 +2614,7 @@
         <v>21</v>
       </c>
       <c r="S13" t="s" s="2">
-        <v>21</v>
+        <v>163</v>
       </c>
       <c r="T13" t="s" s="2">
         <v>21</v>
@@ -2607,13 +2629,13 @@
         <v>21</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>21</v>
@@ -2631,7 +2653,7 @@
         <v>21</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>85</v>
@@ -2646,18 +2668,18 @@
         <v>97</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2680,17 +2702,17 @@
         <v>86</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>21</v>
@@ -2703,7 +2725,7 @@
         <v>21</v>
       </c>
       <c r="T14" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="U14" t="s" s="2">
         <v>21</v>
@@ -2739,7 +2761,7 @@
         <v>21</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -2754,18 +2776,18 @@
         <v>97</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2788,19 +2810,19 @@
         <v>86</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>21</v>
@@ -2825,13 +2847,13 @@
         <v>21</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>21</v>
@@ -2849,7 +2871,7 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -2864,18 +2886,18 @@
         <v>97</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2886,7 +2908,7 @@
         <v>77</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>21</v>
@@ -2898,19 +2920,19 @@
         <v>86</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>21</v>
@@ -2959,7 +2981,7 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -2974,18 +2996,18 @@
         <v>97</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2996,7 +3018,7 @@
         <v>77</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>21</v>
@@ -3008,13 +3030,13 @@
         <v>21</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3065,7 +3087,7 @@
         <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3080,18 +3102,18 @@
         <v>97</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3102,7 +3124,7 @@
         <v>77</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>21</v>
@@ -3114,19 +3136,19 @@
         <v>86</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>21</v>
@@ -3175,7 +3197,7 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -3190,29 +3212,29 @@
         <v>97</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>21</v>
@@ -3224,19 +3246,19 @@
         <v>86</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>21</v>
@@ -3285,7 +3307,7 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -3300,18 +3322,18 @@
         <v>97</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3325,7 +3347,7 @@
         <v>85</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>21</v>
@@ -3334,19 +3356,19 @@
         <v>21</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>21</v>
@@ -3356,7 +3378,7 @@
         <v>21</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>21</v>
+        <v>221</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>21</v>
@@ -3371,13 +3393,11 @@
         <v>21</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="Y20" t="s" s="2">
-        <v>220</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>21</v>
@@ -3395,7 +3415,7 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3410,18 +3430,18 @@
         <v>97</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3444,13 +3464,13 @@
         <v>21</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3501,7 +3521,7 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -3516,7 +3536,7 @@
         <v>97</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>21</v>
@@ -3524,10 +3544,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3541,7 +3561,7 @@
         <v>78</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>21</v>
@@ -3550,16 +3570,16 @@
         <v>21</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3609,7 +3629,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -3618,24 +3638,24 @@
         <v>78</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3658,13 +3678,13 @@
         <v>21</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3715,7 +3735,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -3730,18 +3750,18 @@
         <v>21</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3770,7 +3790,7 @@
         <v>132</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N24" t="s" s="2">
         <v>134</v>
@@ -3823,7 +3843,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -3838,22 +3858,22 @@
         <v>136</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -3875,10 +3895,10 @@
         <v>131</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N25" t="s" s="2">
         <v>134</v>
@@ -3933,7 +3953,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -3956,10 +3976,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3967,13 +3987,13 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>21</v>
@@ -3982,19 +4002,19 @@
         <v>21</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>21</v>
@@ -4019,11 +4039,9 @@
         <v>21</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
         <v>254</v>
       </c>
@@ -4043,7 +4061,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4058,7 +4076,7 @@
         <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>21</v>
@@ -4083,7 +4101,7 @@
         <v>85</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>86</v>
@@ -4176,7 +4194,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
         <v>264</v>
       </c>
@@ -4204,7 +4222,7 @@
         <v>21</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L28" t="s" s="2">
         <v>265</v>
@@ -4303,7 +4321,7 @@
         <v>85</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>21</v>
@@ -4390,7 +4408,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
         <v>274</v>
       </c>
@@ -4418,7 +4436,7 @@
         <v>21</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L30" t="s" s="2">
         <v>275</v>
@@ -4488,7 +4506,7 @@
         <v>85</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>97</v>
@@ -4501,6 +4519,24 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AL30">
+    <filterColumn colId="7">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="27">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI29">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-23T19:34:42+00:00</t>
+    <t>2026-01-26T15:48:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1066" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1066" uniqueCount="284">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T15:48:48+00:00</t>
+    <t>2026-01-28T08:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>**Beschreibung:** Bildet den Medikationsplan eines ELGA Teilnehmers ab. Enthält verordnete Arzneimittel und deren Dosierung in Form von 0..* Medikationsplaneinträgen (AtEmedMedicationRequestPlaneintrag). Die Reihenfolge der Einträge ist fachlich relevant.</t>
+    <t>**Beschreibung:** Bildet den Medikationsplan eines ELGA Teilnehmers ab. Enthält verordnete Arzneimittel und deren Dosierung in Form von 0..* Medikationsplaneinträgen (AtEmedMRPlaneintrag). Die Reihenfolge der Einträge ist fachlich relevant.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -467,7 +467,7 @@
 </t>
   </si>
   <si>
-    <t>Eindeutige Kennung der Liste. Keine Verwendung in der Liste für den Medikationsplan.</t>
+    <t>Business identifier</t>
   </si>
   <si>
     <t>Identifier for the List assigned for business purposes outside the context of FHIR.</t>
@@ -580,6 +580,15 @@
     <t>Lists often contain subsets of resources rather than an exhaustive list.  The code identifies what type of subset is included.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://snomed.info/sct"/&gt;
+    &lt;code value="736378000"/&gt;
+    &lt;display value="Medikationsplan"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>example</t>
   </si>
   <si>
@@ -598,11 +607,11 @@
     <t>List.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|4.0.1|Group|4.0.1|Device|4.0.1|Location|4.0.1)
+    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-patient)
 </t>
   </si>
   <si>
-    <t>Keine Verwendung in der Liste für den Medikationsplan.</t>
+    <t>If all resources have the same subject</t>
   </si>
   <si>
     <t>The common subject (or patient) of the resources that are in the list if there is one.</t>
@@ -627,6 +636,9 @@
 </t>
   </si>
   <si>
+    <t>Keine Verwendung in der Liste für den Medikationsplan.</t>
+  </si>
+  <si>
     <t>The encounter that is the context in which this list was created.</t>
   </si>
   <si>
@@ -668,7 +680,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Patient|4.0.1|Device|4.0.1)
+    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitionerRole)
 </t>
   </si>
   <si>
@@ -725,7 +737,7 @@
 </t>
   </si>
   <si>
-    <t>Comments about the list</t>
+    <t>Freitextliche Anmerkungen zum Medikationsplan.</t>
   </si>
   <si>
     <t>Comments that apply to the overall list.</t>
@@ -823,7 +835,7 @@
 </t>
   </si>
   <si>
-    <t>Gibt an, ob der referenzierte Medikationsplaneintrag aus dem Medikationsplan entfernt wurde.</t>
+    <t>Gibt an, ob der referenzierte Medikationsplaneintrag aus dem Medikationsplan entfernt wurde. Unklar, ob Löschen so abgebildet werden soll.</t>
   </si>
   <si>
     <t>True if this item is marked as deleted in the list.</t>
@@ -848,7 +860,7 @@
     <t>List.entry.date</t>
   </si>
   <si>
-    <t>When item added to list</t>
+    <t>Datum der Aufnahme des Medikationsplaneintrags in den Medikationsplan. Fachlich zu klären.</t>
   </si>
   <si>
     <t>When this item was added to the list.</t>
@@ -863,7 +875,7 @@
     <t>List.entry.item</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-medicationrequest-planeintrag)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-mr-planeintrag)
 </t>
   </si>
   <si>
@@ -879,7 +891,7 @@
     <t>List.emptyReason</t>
   </si>
   <si>
-    <t>Grund, warum die Liste keine Einträge enthält. Zu prüfen, ob/wie in Liste des Medikationsplan verwendet.</t>
+    <t>Intitalzustand: notstarted Grund, TODO: code für "Patient nimmt derzeit keine Medikamente ein".</t>
   </si>
   <si>
     <t>If the list is empty, why the list is empty.</t>
@@ -1235,7 +1247,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="82.0390625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="140.921875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2782,7 +2794,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>175</v>
       </c>
@@ -2795,13 +2807,13 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>21</v>
@@ -2832,7 +2844,7 @@
         <v>21</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>21</v>
+        <v>181</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>21</v>
@@ -2847,13 +2859,13 @@
         <v>21</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>21</v>
@@ -2886,18 +2898,18 @@
         <v>97</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="16" hidden="true">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2905,13 +2917,13 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>21</v>
@@ -2920,19 +2932,19 @@
         <v>86</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>21</v>
@@ -2981,7 +2993,7 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -2996,18 +3008,18 @@
         <v>97</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3030,13 +3042,13 @@
         <v>21</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3087,7 +3099,7 @@
         <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3102,18 +3114,18 @@
         <v>97</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="18" hidden="true">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3121,13 +3133,13 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>21</v>
@@ -3136,19 +3148,19 @@
         <v>86</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>21</v>
@@ -3197,7 +3209,7 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -3212,32 +3224,32 @@
         <v>97</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="19" hidden="true">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>21</v>
@@ -3246,19 +3258,19 @@
         <v>86</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>21</v>
@@ -3307,7 +3319,7 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -3322,18 +3334,18 @@
         <v>97</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3341,7 +3353,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>85</v>
@@ -3359,16 +3371,16 @@
         <v>176</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>21</v>
@@ -3378,7 +3390,7 @@
         <v>21</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>21</v>
@@ -3397,7 +3409,7 @@
       </c>
       <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>21</v>
@@ -3415,7 +3427,7 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3430,18 +3442,18 @@
         <v>97</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3455,7 +3467,7 @@
         <v>78</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>21</v>
@@ -3464,13 +3476,13 @@
         <v>21</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3521,7 +3533,7 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -3536,7 +3548,7 @@
         <v>97</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>21</v>
@@ -3544,10 +3556,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3570,16 +3582,16 @@
         <v>21</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3629,7 +3641,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -3638,13 +3650,13 @@
         <v>78</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>21</v>
@@ -3652,10 +3664,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3681,10 +3693,10 @@
         <v>169</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3735,7 +3747,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -3750,7 +3762,7 @@
         <v>21</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>21</v>
@@ -3758,10 +3770,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3790,7 +3802,7 @@
         <v>132</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="N24" t="s" s="2">
         <v>134</v>
@@ -3843,7 +3855,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -3858,7 +3870,7 @@
         <v>136</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>21</v>
@@ -3866,14 +3878,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -3895,10 +3907,10 @@
         <v>131</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="N25" t="s" s="2">
         <v>134</v>
@@ -3953,7 +3965,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -3976,10 +3988,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4005,16 +4017,16 @@
         <v>176</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>21</v>
@@ -4043,7 +4055,7 @@
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>21</v>
@@ -4061,7 +4073,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4084,10 +4096,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4110,71 +4122,71 @@
         <v>21</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="P27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q27" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="R27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="M27" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="P27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q27" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="R27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>255</v>
-      </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
       </c>
@@ -4182,24 +4194,24 @@
         <v>85</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4213,7 +4225,7 @@
         <v>85</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>21</v>
@@ -4222,17 +4234,17 @@
         <v>21</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>21</v>
@@ -4281,7 +4293,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -4296,7 +4308,7 @@
         <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>21</v>
@@ -4304,10 +4316,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4330,13 +4342,13 @@
         <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4387,7 +4399,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>85</v>
@@ -4402,18 +4414,18 @@
         <v>97</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4427,7 +4439,7 @@
         <v>85</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>21</v>
@@ -4439,16 +4451,16 @@
         <v>176</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>21</v>
@@ -4476,10 +4488,10 @@
         <v>109</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>21</v>
@@ -4497,7 +4509,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -4506,13 +4518,13 @@
         <v>85</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T08:09:20+00:00</t>
+    <t>2026-01-28T19:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T19:29:09+00:00</t>
+    <t>2026-01-29T08:16:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1066" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1066" uniqueCount="283">
   <si>
     <t>Property</t>
   </si>
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>ELGA e-Medikation Medikationsplan</t>
+    <t>ELGA e-Med Medikationsplan</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T08:16:48+00:00</t>
+    <t>2026-01-29T15:27:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,9 @@
     <t>Description</t>
   </si>
   <si>
-    <t>**Beschreibung:** Bildet den Medikationsplan eines ELGA Teilnehmers ab. Enthält verordnete Arzneimittel und deren Dosierung in Form von 0..* Medikationsplaneinträgen (AtEmedMRPlaneintrag). Die Reihenfolge der Einträge ist fachlich relevant.</t>
+    <t>**Beschreibung:** Bildet den Medikationsplan eines ELGA Teilnehmers ab ("List"-Ressource). 
+Die Liste beinhaltet Referenzen auf 0..* Medikationsplaneinträge (MedicationRequests), die alle verordneten Arzneimitteln und deren Dosierung abbilden.
+Jedes Listenelement enthält einen Änderungsstatus (weitere Elemente sind noch zu klären). Die Reihenfolge der Listenelemente wird duch den User festgelegt.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -467,7 +469,7 @@
 </t>
   </si>
   <si>
-    <t>Business identifier</t>
+    <t>Eindeutige Kennung der Liste. Verwendung zu prüfen.</t>
   </si>
   <si>
     <t>Identifier for the List assigned for business purposes outside the context of FHIR.</t>
@@ -522,9 +524,6 @@
   </si>
   <si>
     <t>Lists are used in various ways, and it must be known in what way it is safe to use them.</t>
-  </si>
-  <si>
-    <t>working</t>
   </si>
   <si>
     <t>The processing mode that applies to this list.</t>
@@ -2378,7 +2377,7 @@
         <v>77</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>21</v>
@@ -2626,7 +2625,7 @@
         <v>21</v>
       </c>
       <c r="S13" t="s" s="2">
-        <v>163</v>
+        <v>21</v>
       </c>
       <c r="T13" t="s" s="2">
         <v>21</v>
@@ -2644,10 +2643,10 @@
         <v>153</v>
       </c>
       <c r="Y13" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="Z13" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>21</v>
@@ -2680,18 +2679,18 @@
         <v>97</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AL13" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>167</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2714,17 +2713,17 @@
         <v>86</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="L14" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="M14" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>21</v>
@@ -2737,7 +2736,7 @@
         <v>21</v>
       </c>
       <c r="T14" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="U14" t="s" s="2">
         <v>21</v>
@@ -2773,7 +2772,7 @@
         <v>21</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -2788,7 +2787,7 @@
         <v>97</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>21</v>
@@ -2796,10 +2795,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2822,19 +2821,19 @@
         <v>86</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="N15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>21</v>
@@ -2844,29 +2843,29 @@
         <v>21</v>
       </c>
       <c r="S15" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="T15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X15" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="T15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X15" t="s" s="2">
+      <c r="Y15" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="Y15" t="s" s="2">
+      <c r="Z15" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="Z15" t="s" s="2">
-        <v>184</v>
-      </c>
       <c r="AA15" t="s" s="2">
         <v>21</v>
       </c>
@@ -2883,7 +2882,7 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -2898,18 +2897,18 @@
         <v>97</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AL15" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>186</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2932,19 +2931,19 @@
         <v>86</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="N16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>192</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>21</v>
@@ -2993,7 +2992,7 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3008,18 +3007,18 @@
         <v>97</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AL16" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="AL16" t="s" s="2">
-        <v>194</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3042,13 +3041,13 @@
         <v>21</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3099,7 +3098,7 @@
         <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3114,18 +3113,18 @@
         <v>97</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AL17" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>200</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3148,19 +3147,19 @@
         <v>86</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>21</v>
@@ -3209,7 +3208,7 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -3224,22 +3223,22 @@
         <v>97</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AL18" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>208</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3258,19 +3257,19 @@
         <v>86</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="N19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>21</v>
@@ -3319,7 +3318,7 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -3334,18 +3333,18 @@
         <v>97</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AL19" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AL19" t="s" s="2">
-        <v>217</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3368,19 +3367,19 @@
         <v>21</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="N20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>21</v>
@@ -3390,7 +3389,7 @@
         <v>21</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>21</v>
@@ -3409,7 +3408,7 @@
       </c>
       <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>21</v>
@@ -3427,7 +3426,7 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3442,7 +3441,7 @@
         <v>97</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>21</v>
@@ -3450,10 +3449,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3476,13 +3475,13 @@
         <v>21</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3533,7 +3532,7 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -3548,7 +3547,7 @@
         <v>97</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>21</v>
@@ -3556,10 +3555,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3582,16 +3581,16 @@
         <v>21</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3641,7 +3640,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -3650,13 +3649,13 @@
         <v>78</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>21</v>
@@ -3664,10 +3663,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3690,13 +3689,13 @@
         <v>21</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>239</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3747,22 +3746,22 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK23" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="AG23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH23" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI23" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ23" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AK23" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>21</v>
@@ -3770,10 +3769,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3802,7 +3801,7 @@
         <v>132</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="N24" t="s" s="2">
         <v>134</v>
@@ -3855,7 +3854,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -3870,7 +3869,7 @@
         <v>136</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>21</v>
@@ -3878,14 +3877,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -3907,10 +3906,10 @@
         <v>131</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="N25" t="s" s="2">
         <v>134</v>
@@ -3965,7 +3964,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -3988,10 +3987,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4014,19 +4013,19 @@
         <v>21</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>21</v>
@@ -4055,7 +4054,7 @@
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>21</v>
@@ -4073,7 +4072,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4088,7 +4087,7 @@
         <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>21</v>
@@ -4096,10 +4095,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4122,85 +4121,85 @@
         <v>21</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="O27" t="s" s="2">
+      <c r="P27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q27" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="P27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q27" t="s" s="2">
+      <c r="R27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF27" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI27" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="R27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="AG27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH27" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI27" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>21</v>
@@ -4208,10 +4207,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4234,17 +4233,17 @@
         <v>21</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>21</v>
@@ -4293,7 +4292,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -4308,7 +4307,7 @@
         <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>21</v>
@@ -4316,10 +4315,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4342,13 +4341,13 @@
         <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4399,7 +4398,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>85</v>
@@ -4414,7 +4413,7 @@
         <v>97</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>21</v>
@@ -4422,10 +4421,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4448,19 +4447,19 @@
         <v>21</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="N30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>21</v>
@@ -4488,11 +4487,11 @@
         <v>109</v>
       </c>
       <c r="Y30" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="Z30" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="Z30" t="s" s="2">
-        <v>282</v>
-      </c>
       <c r="AA30" t="s" s="2">
         <v>21</v>
       </c>
@@ -4509,7 +4508,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -4518,13 +4517,13 @@
         <v>85</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1066" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1066" uniqueCount="282">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T15:27:43+00:00</t>
+    <t>2026-01-30T14:55:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,9 +87,9 @@
     <t>Description</t>
   </si>
   <si>
-    <t>**Beschreibung:** Bildet den Medikationsplan eines ELGA Teilnehmers ab ("List"-Ressource). 
-Die Liste beinhaltet Referenzen auf 0..* Medikationsplaneinträge (MedicationRequests), die alle verordneten Arzneimitteln und deren Dosierung abbilden.
-Jedes Listenelement enthält einen Änderungsstatus (weitere Elemente sind noch zu klären). Die Reihenfolge der Listenelemente wird duch den User festgelegt.</t>
+    <t>**Beschreibung:** Bildet den Medikationsplan eines ELGA-Teilnehmers ab ("List"-Ressource). 
+Die Liste beinhaltet Referenzen auf 0..* Medikationsplaneinträge (MedicationRequests), die alle verordneten Arzneimittel und deren Dosierung abbilden.
+Die Reihenfolge der Listenelemente kann duch den User festgelegt werden. Jedes Listenelement enthält einen Änderungsstatus (weitere Elemente sind noch zu klären).</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -491,9 +491,6 @@
   </si>
   <si>
     <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
-  </si>
-  <si>
-    <t>current</t>
   </si>
   <si>
     <t>required</t>
@@ -704,7 +701,8 @@
     <t>List.orderedBy</t>
   </si>
   <si>
-    <t>Die Reihenfolge der Einträge im Medikationsplan ist fachlich relevant und wird durch den Ersteller der Liste vorgegeben. Mögliche Codes: user | system | event-date | entry-date| priority | alphabetic | category | patient.</t>
+    <t>Die Reihenfolge der Einträge im Medikationsplan ist fachlich relevant und wird durch den Erseller der Liste vorgegeben. 
+Mögliche Codes: user | system | event-date | entry-date| priority | alphabetic | category | patient.</t>
   </si>
   <si>
     <t>What order applies to the items in the list.</t>
@@ -736,7 +734,7 @@
 </t>
   </si>
   <si>
-    <t>Freitextliche Anmerkungen zum Medikationsplan.</t>
+    <t>Freitextliche Anmerkungen zum Medikationsplan. Prüfen hinsichtlich Korrekturvermerk.</t>
   </si>
   <si>
     <t>Comments that apply to the overall list.</t>
@@ -812,7 +810,7 @@
     <t>List.entry.flag</t>
   </si>
   <si>
-    <t>Kennzeichnet die Art der Änderung des Medikationsplaneintrags</t>
+    <t>Kennzeichnet die Art der Änderung des Medikationsplaneintrags.</t>
   </si>
   <si>
     <t>The flag allows the system constructing the list to indicate the role and significance of the item in the list.</t>
@@ -890,7 +888,7 @@
     <t>List.emptyReason</t>
   </si>
   <si>
-    <t>Intitalzustand: notstarted Grund, TODO: code für "Patient nimmt derzeit keine Medikamente ein".</t>
+    <t>Intitalzustand: notstarted Grund, TODO: Code für "Patient nimmt derzeit keine Medikamente ein".</t>
   </si>
   <si>
     <t>If the list is empty, why the list is empty.</t>
@@ -2361,7 +2359,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>142</v>
       </c>
@@ -2380,7 +2378,7 @@
         <v>85</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>21</v>
@@ -2515,28 +2513,28 @@
         <v>21</v>
       </c>
       <c r="S12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X12" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="T12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X12" t="s" s="2">
+      <c r="Y12" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="Y12" t="s" s="2">
+      <c r="Z12" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>21</v>
@@ -2569,18 +2567,18 @@
         <v>97</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AL12" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>157</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2606,16 +2604,16 @@
         <v>105</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="N13" t="s" s="2">
+      <c r="O13" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>162</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>21</v>
@@ -2640,14 +2638,14 @@
         <v>21</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Y13" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="Z13" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="Z13" t="s" s="2">
-        <v>164</v>
-      </c>
       <c r="AA13" t="s" s="2">
         <v>21</v>
       </c>
@@ -2664,7 +2662,7 @@
         <v>21</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>85</v>
@@ -2679,18 +2677,18 @@
         <v>97</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AL13" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>166</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2713,17 +2711,17 @@
         <v>86</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L14" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="M14" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>21</v>
@@ -2736,7 +2734,7 @@
         <v>21</v>
       </c>
       <c r="T14" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="U14" t="s" s="2">
         <v>21</v>
@@ -2772,7 +2770,7 @@
         <v>21</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -2787,7 +2785,7 @@
         <v>97</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>21</v>
@@ -2795,10 +2793,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2821,19 +2819,19 @@
         <v>86</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="N15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>21</v>
@@ -2843,29 +2841,29 @@
         <v>21</v>
       </c>
       <c r="S15" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="T15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X15" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="T15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X15" t="s" s="2">
+      <c r="Y15" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="Y15" t="s" s="2">
+      <c r="Z15" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="Z15" t="s" s="2">
-        <v>183</v>
-      </c>
       <c r="AA15" t="s" s="2">
         <v>21</v>
       </c>
@@ -2882,7 +2880,7 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -2897,18 +2895,18 @@
         <v>97</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AL15" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>185</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2931,19 +2929,19 @@
         <v>86</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="N16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>21</v>
@@ -2992,7 +2990,7 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3007,18 +3005,18 @@
         <v>97</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AL16" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="AL16" t="s" s="2">
-        <v>193</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3041,13 +3039,13 @@
         <v>21</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3098,7 +3096,7 @@
         <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3113,18 +3111,18 @@
         <v>97</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AL17" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>199</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3147,19 +3145,19 @@
         <v>86</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>21</v>
@@ -3208,7 +3206,7 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -3223,22 +3221,22 @@
         <v>97</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AL18" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>207</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3257,19 +3255,19 @@
         <v>86</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="N19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>21</v>
@@ -3318,7 +3316,7 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -3333,18 +3331,18 @@
         <v>97</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AL19" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="AL19" t="s" s="2">
-        <v>216</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3367,19 +3365,19 @@
         <v>21</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="N20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>21</v>
@@ -3389,7 +3387,7 @@
         <v>21</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>21</v>
@@ -3404,11 +3402,11 @@
         <v>21</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>21</v>
@@ -3426,7 +3424,7 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3441,7 +3439,7 @@
         <v>97</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>21</v>
@@ -3449,10 +3447,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3475,13 +3473,13 @@
         <v>21</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3532,7 +3530,7 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -3547,7 +3545,7 @@
         <v>97</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>21</v>
@@ -3555,10 +3553,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3581,16 +3579,16 @@
         <v>21</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3640,7 +3638,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -3649,13 +3647,13 @@
         <v>78</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>21</v>
@@ -3663,10 +3661,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3689,13 +3687,13 @@
         <v>21</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3746,22 +3744,22 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK23" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="AG23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH23" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI23" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ23" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AK23" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>21</v>
@@ -3769,10 +3767,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3801,7 +3799,7 @@
         <v>132</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="N24" t="s" s="2">
         <v>134</v>
@@ -3854,7 +3852,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -3869,7 +3867,7 @@
         <v>136</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>21</v>
@@ -3877,14 +3875,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -3906,10 +3904,10 @@
         <v>131</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="N25" t="s" s="2">
         <v>134</v>
@@ -3964,7 +3962,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -3987,10 +3985,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4013,19 +4011,19 @@
         <v>21</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>21</v>
@@ -4050,11 +4048,11 @@
         <v>21</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>21</v>
@@ -4072,7 +4070,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4087,7 +4085,7 @@
         <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>21</v>
@@ -4095,10 +4093,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4121,85 +4119,85 @@
         <v>21</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="O27" t="s" s="2">
+      <c r="P27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q27" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="P27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q27" t="s" s="2">
+      <c r="R27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF27" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI27" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="R27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="AG27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH27" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI27" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>21</v>
@@ -4207,10 +4205,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4233,17 +4231,17 @@
         <v>21</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>21</v>
@@ -4292,7 +4290,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -4307,7 +4305,7 @@
         <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>21</v>
@@ -4315,10 +4313,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4341,13 +4339,13 @@
         <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4398,7 +4396,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>85</v>
@@ -4413,7 +4411,7 @@
         <v>97</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>21</v>
@@ -4421,10 +4419,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4447,19 +4445,19 @@
         <v>21</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="N30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>21</v>
@@ -4487,11 +4485,11 @@
         <v>109</v>
       </c>
       <c r="Y30" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="Z30" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="Z30" t="s" s="2">
-        <v>281</v>
-      </c>
       <c r="AA30" t="s" s="2">
         <v>21</v>
       </c>
@@ -4508,7 +4506,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -4517,13 +4515,13 @@
         <v>85</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T14:55:57+00:00</t>
+    <t>2026-02-09T17:27:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T17:27:03+00:00</t>
+    <t>2026-02-10T17:53:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -89,7 +89,8 @@
   <si>
     <t>**Beschreibung:** Bildet den Medikationsplan eines ELGA-Teilnehmers ab ("List"-Ressource). 
 Die Liste beinhaltet Referenzen auf 0..* Medikationsplaneinträge (MedicationRequests), die alle verordneten Arzneimittel und deren Dosierung abbilden.
-Die Reihenfolge der Listenelemente kann duch den User festgelegt werden. Jedes Listenelement enthält einen Änderungsstatus (weitere Elemente sind noch zu klären).</t>
+Die Reihenfolge der Listenelemente kann duch den User festgelegt werden. Jedes Listenelement enthält einen Änderungsstatus (weitere Elemente sind noch zu klären).
+TODO: Invariante, dass überall in der List der gleiche Patient enthalten sein muss</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -469,7 +470,7 @@
 </t>
   </si>
   <si>
-    <t>Eindeutige Kennung der Liste. Verwendung zu prüfen.</t>
+    <t>Eindeutige Kennung der Liste / des Medikationsplans. Verwendung zu prüfen.</t>
   </si>
   <si>
     <t>Identifier for the List assigned for business purposes outside the context of FHIR.</t>
@@ -484,7 +485,7 @@
     <t>List.status</t>
   </si>
   <si>
-    <t>Der Medikationsplan ist aktuell: current | retired | entered-in-error. https://hl7.org/fhir/R4/valueset-list-status.html</t>
+    <t>Verpflichtende Angabe: current | retired | entered-in-error. https://hl7.org/fhir/R4/valueset-list-status.html</t>
   </si>
   <si>
     <t>Indicates the current state of this list.</t>
@@ -511,7 +512,8 @@
     <t>List.mode</t>
   </si>
   <si>
-    <t>Der Medikationsplan ist ein Arbeitsdokument: working | snapshot | changes. https://hl7.org/fhir/R4/valueset-list-mode.html</t>
+    <t>Verpflichtende Angabe: working | snapshot | changes. https://hl7.org/fhir/R4/valueset-list-mode.html
+Der Medikationsplan ist ein laufend gepflegtes Dokument: working</t>
   </si>
   <si>
     <t>How this list was prepared - whether it is a working list that is suitable for being maintained on an ongoing basis, or if it represents a snapshot of a list of items from another source, or whether it is a prepared list where items may be marked as added, modified or deleted.</t>
@@ -542,7 +544,7 @@
 </t>
   </si>
   <si>
-    <t>Descriptive name for the list</t>
+    <t>Titel der Liste. Verwendung zu prüfen.</t>
   </si>
   <si>
     <t>A label for the list assigned by the author.</t>
@@ -607,7 +609,7 @@
 </t>
   </si>
   <si>
-    <t>If all resources have the same subject</t>
+    <t>Österreichischer Patient für den der Medikationsplan erstellt wird.</t>
   </si>
   <si>
     <t>The common subject (or patient) of the resources that are in the list if there is one.</t>
@@ -632,7 +634,7 @@
 </t>
   </si>
   <si>
-    <t>Keine Verwendung in der Liste für den Medikationsplan.</t>
+    <t>Verwendung zu prüfen.</t>
   </si>
   <si>
     <t>The encounter that is the context in which this list was created.</t>
@@ -651,7 +653,7 @@
 </t>
   </si>
   <si>
-    <t>Letzte Aktualisierung der Liste des Medikationsplans.</t>
+    <t>Letzte Aktualisierung des Medikationsplans.</t>
   </si>
   <si>
     <t>The date that the list was prepared.</t>
@@ -680,7 +682,7 @@
 </t>
   </si>
   <si>
-    <t>Ersteller der Liste des Medikationsplans.</t>
+    <t>Ersteller des Medikationsplans.</t>
   </si>
   <si>
     <t>The entity responsible for deciding what the contents of the list were. Where the list was created by a human, this is the same as the author of the list.</t>
@@ -701,8 +703,8 @@
     <t>List.orderedBy</t>
   </si>
   <si>
-    <t>Die Reihenfolge der Einträge im Medikationsplan ist fachlich relevant und wird durch den Erseller der Liste vorgegeben. 
-Mögliche Codes: user | system | event-date | entry-date| priority | alphabetic | category | patient.</t>
+    <t>Die Reihenfolge der Einträge im Medikationsplan ist fachlich relevant und wird durch den Ersteller vorgegeben. 
+Mögliche Codes: user | system | event-date | entry-date| priority | alphabetic | category | patient (einschränken?)</t>
   </si>
   <si>
     <t>What order applies to the items in the list.</t>
@@ -810,7 +812,7 @@
     <t>List.entry.flag</t>
   </si>
   <si>
-    <t>Kennzeichnet die Art der Änderung des Medikationsplaneintrags.</t>
+    <t>Kennzeichnet die Art der Änderung des Medikationsplaneintrags: zB Unchanged | Changed | Cancelled | Prescribed | Ceased | Suspended.</t>
   </si>
   <si>
     <t>The flag allows the system constructing the list to indicate the role and significance of the item in the list.</t>
@@ -832,7 +834,7 @@
 </t>
   </si>
   <si>
-    <t>Gibt an, ob der referenzierte Medikationsplaneintrag aus dem Medikationsplan entfernt wurde. Unklar, ob Löschen so abgebildet werden soll.</t>
+    <t>Gibt an, ob der referenzierte Medikationsplaneintrag zur Entfernung markiert wurde. Unklar, ob Löschen so abgebildet werden soll.</t>
   </si>
   <si>
     <t>True if this item is marked as deleted in the list.</t>
@@ -857,7 +859,7 @@
     <t>List.entry.date</t>
   </si>
   <si>
-    <t>Datum der Aufnahme des Medikationsplaneintrags in den Medikationsplan. Fachlich zu klären.</t>
+    <t>Datum der Aufnahme des Medikationsplaneintrags. Fachlich zu klären.</t>
   </si>
   <si>
     <t>When this item was added to the list.</t>
@@ -888,7 +890,7 @@
     <t>List.emptyReason</t>
   </si>
   <si>
-    <t>Intitalzustand: notstarted Grund, TODO: Code für "Patient nimmt derzeit keine Medikamente ein".</t>
+    <t>Grund, warum der Medikationsplan noch leer ist: Intitalzustand: notstarted, TODO: Code für "Patient nimmt derzeit keine Medikamente ein".</t>
   </si>
   <si>
     <t>If the list is empty, why the list is empty.</t>
@@ -2699,7 +2701,7 @@
         <v>77</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-10T17:53:58+00:00</t>
+    <t>2026-02-12T16:23:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-12T16:23:56+00:00</t>
+    <t>2026-02-16T10:10:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T10:10:16+00:00</t>
+    <t>2026-02-16T15:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1066" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="281">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T15:59:40+00:00</t>
+    <t>2026-02-17T17:15:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -470,7 +470,7 @@
 </t>
   </si>
   <si>
-    <t>Eindeutige Kennung der Liste / des Medikationsplans. Verwendung zu prüfen.</t>
+    <t>Logischer Identfier der Liste / des Medikationsplans. Verwendung zu prüfen.</t>
   </si>
   <si>
     <t>Identifier for the List assigned for business purposes outside the context of FHIR.</t>
@@ -609,7 +609,8 @@
 </t>
   </si>
   <si>
-    <t>Österreichischer Patient für den der Medikationsplan erstellt wird.</t>
+    <t>Patient, für den der Medikationsplan erstellt werden soll, der über den 
+Zentralen Patientenindex identifizierbar und Teilnehmer von ELGA e-Medikation ist.</t>
   </si>
   <si>
     <t>The common subject (or patient) of the resources that are in the list if there is one.</t>
@@ -682,7 +683,9 @@
 </t>
   </si>
   <si>
-    <t>Ersteller des Medikationsplans.</t>
+    <t>Arzt oder Ärztin, die den Medikationsplans erstellt und für den Inhalt verantwortlich ist. 
+Eindeutig identifiziert über den GDA-Index und berechtigt auf die ELGA e-Medikation 
+des Patienten zuzugreifen.</t>
   </si>
   <si>
     <t>The entity responsible for deciding what the contents of the list were. Where the list was created by a human, this is the same as the author of the list.</t>
@@ -704,7 +707,7 @@
   </si>
   <si>
     <t>Die Reihenfolge der Einträge im Medikationsplan ist fachlich relevant und wird durch den Ersteller vorgegeben. 
-Mögliche Codes: user | system | event-date | entry-date| priority | alphabetic | category | patient (einschränken?)</t>
+Mögliche Codes: user | system | event-date | entry-date| priority | alphabetic | category | patient (TODO: nur user oder andere Reihenfolge ermöglichen?)</t>
   </si>
   <si>
     <t>What order applies to the items in the list.</t>
@@ -736,7 +739,7 @@
 </t>
   </si>
   <si>
-    <t>Freitextliche Anmerkungen zum Medikationsplan. Prüfen hinsichtlich Korrekturvermerk.</t>
+    <t>Freitextliche Anmerkungen zum Medikationsplan. TODO: prüfen, ob fachlich sinnvoll.</t>
   </si>
   <si>
     <t>Comments that apply to the overall list.</t>
@@ -834,7 +837,7 @@
 </t>
   </si>
   <si>
-    <t>Gibt an, ob der referenzierte Medikationsplaneintrag zur Entfernung markiert wurde. Unklar, ob Löschen so abgebildet werden soll.</t>
+    <t>Gibt an, ob der referenzierte Medikationsplaneintrag zur Entfernung markiert wurde. Unklar, ob Löschen so abgebildet werden soll oder einfach der Eintrag nicht mehr enthalten ist.</t>
   </si>
   <si>
     <t>True if this item is marked as deleted in the list.</t>
@@ -890,7 +893,10 @@
     <t>List.emptyReason</t>
   </si>
   <si>
-    <t>Grund, warum der Medikationsplan noch leer ist: Intitalzustand: notstarted, TODO: Code für "Patient nimmt derzeit keine Medikamente ein".</t>
+    <t>Begründung, warum der Medikationsplan leer ist: 
+https://hl7.org/fhir/R4/valueset-list-empty-reason.html eingeschränkt auf: &lt;vbr&gt;
+    - notstarted: Intitalzustand &lt;br&gt;
+    - nilknown: Patient nimmt derzeit keine Medikamente ein</t>
   </si>
   <si>
     <t>If the list is empty, why the list is empty.</t>
@@ -902,10 +908,7 @@
     <t>Allows capturing things like "none exist" or "not asked" which can be important for most lists.</t>
   </si>
   <si>
-    <t>If a list is empty, why it is empty.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/list-empty-reason|4.0.1</t>
+    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/MedikationsplanEmptyReasonVS</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ,code&lt;ListEmptyReason].value[type=CD]</t>
@@ -1261,7 +1264,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="36.34375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="41.86328125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="59.109375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
@@ -4484,13 +4487,11 @@
         <v>21</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="Y30" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="Y30" s="2"/>
+      <c r="Z30" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="Z30" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>21</v>
@@ -4523,7 +4524,7 @@
         <v>97</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T17:15:57+00:00</t>
+    <t>2026-02-20T10:02:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-20T10:02:53+00:00</t>
+    <t>2026-02-23T08:57:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T08:57:08+00:00</t>
+    <t>2026-02-23T17:25:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T17:25:44+00:00</t>
+    <t>2026-02-26T16:36:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>**Beschreibung:** Bildet den Medikationsplan eines ELGA-Teilnehmers ab ("List"-Ressource). 
+    <t>Bildet den Medikationsplan eines ELGA-Teilnehmers ab ("List"-Ressource). 
 Die Liste beinhaltet Referenzen auf 0..* Medikationsplaneinträge (MedicationRequests), die alle verordneten Arzneimittel und deren Dosierung abbilden.
 Die Reihenfolge der Listenelemente kann duch den User festgelegt werden. Jedes Listenelement enthält einen Änderungsstatus (weitere Elemente sind noch zu klären).
 TODO: Invariante, dass überall in der List der gleiche Patient enthalten sein muss</t>
@@ -679,13 +679,13 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitionerRole)
+    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitionerRole|Device)
 </t>
   </si>
   <si>
     <t>Arzt oder Ärztin, die den Medikationsplans erstellt und für den Inhalt verantwortlich ist. 
 Eindeutig identifiziert über den GDA-Index und berechtigt auf die ELGA e-Medikation 
-des Patienten zuzugreifen.</t>
+des Patienten zuzugreifen. Device nur für initiale Erstellung durch die Fachanwendung.</t>
   </si>
   <si>
     <t>The entity responsible for deciding what the contents of the list were. Where the list was created by a human, this is the same as the author of the list.</t>
@@ -1249,7 +1249,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="140.921875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="146.828125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T16:36:39+00:00</t>
+    <t>2026-03-03T08:59:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -679,13 +679,13 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitionerRole|Device)
+    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitionerRole|Device|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-patient)
 </t>
   </si>
   <si>
     <t>Arzt oder Ärztin, die den Medikationsplans erstellt und für den Inhalt verantwortlich ist. 
 Eindeutig identifiziert über den GDA-Index und berechtigt auf die ELGA e-Medikation 
-des Patienten zuzugreifen. Device nur für initiale Erstellung durch die Fachanwendung.</t>
+des Patienten zuzugreifen. Device nur für initiale Erstellung durch die Fachanwendung. Patient nur zur Änderung der Reihenfolge der Planeinträge oder nachdem er Einträge gelöscht hat.</t>
   </si>
   <si>
     <t>The entity responsible for deciding what the contents of the list were. Where the list was created by a human, this is the same as the author of the list.</t>
@@ -1249,7 +1249,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="146.828125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="207.19921875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T08:59:33+00:00</t>
+    <t>2026-03-03T14:03:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T14:03:22+00:00</t>
+    <t>2026-03-05T12:55:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T12:55:37+00:00</t>
+    <t>2026-03-05T13:31:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T13:31:59+00:00</t>
+    <t>2026-03-06T12:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T12:22:28+00:00</t>
+    <t>2026-03-06T14:18:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T14:18:10+00:00</t>
+    <t>2026-03-09T08:14:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T08:14:04+00:00</t>
+    <t>2026-03-09T10:03:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T10:03:26+00:00</t>
+    <t>2026-03-09T11:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T11:27:52+00:00</t>
+    <t>2026-03-10T08:28:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T08:28:41+00:00</t>
+    <t>2026-03-10T11:00:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T11:00:19+00:00</t>
+    <t>2026-03-10T11:31:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T11:31:06+00:00</t>
+    <t>2026-03-16T16:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -582,7 +582,7 @@
   &lt;coding&gt;
     &lt;system value="http://snomed.info/sct"/&gt;
     &lt;code value="736378000"/&gt;
-    &lt;display value="Medikationsplan"/&gt;
+    &lt;display value="Medication management plan (record artifact)"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T16:50:24+00:00</t>
+    <t>2026-03-19T16:44:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T16:44:44+00:00</t>
+    <t>2026-03-20T13:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T13:50:58+00:00</t>
+    <t>2026-03-20T15:30:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T15:30:14+00:00</t>
+    <t>2026-03-24T10:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -89,8 +89,7 @@
   <si>
     <t>Bildet den Medikationsplan eines ELGA-Teilnehmers ab ("List"-Ressource). 
 Die Liste beinhaltet Referenzen auf 0..* Medikationsplaneinträge (MedicationRequests), die alle verordneten Arzneimittel und deren Dosierung abbilden.
-Die Reihenfolge der Listenelemente kann duch den User festgelegt werden. Jedes Listenelement enthält einen Änderungsstatus (weitere Elemente sind noch zu klären).
-TODO: Invariante, dass überall in der List der gleiche Patient enthalten sein muss</t>
+Die Reihenfolge der Listenelemente kann duch den User festgelegt werden. Jedes Listenelement enthält einen Änderungsstatus.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -862,7 +861,7 @@
     <t>List.entry.date</t>
   </si>
   <si>
-    <t>Datum der Aufnahme des Medikationsplaneintrags. Fachlich zu klären.</t>
+    <t>Datum der Aufnahme / Änderung des Medikationsplaneintrags. Fachlich zu klären.</t>
   </si>
   <si>
     <t>When this item was added to the list.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="282">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T10:00:40+00:00</t>
+    <t>2026-03-24T15:12:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -484,7 +484,9 @@
     <t>List.status</t>
   </si>
   <si>
-    <t>Verpflichtende Angabe: current | retired | entered-in-error. https://hl7.org/fhir/R4/valueset-list-status.html</t>
+    <t>Verpflichtende Angabe: current | retired. https://hl7.org/fhir/R4/valueset-list-status.html
+TODO: retired nach Ableben des Patienten bis Ende der Aufbewahrungsfrist? automatisch gesetzt?
+entered-in-error nicht sinnvoll</t>
   </si>
   <si>
     <t>Indicates the current state of this list.</t>
@@ -512,7 +514,7 @@
   </si>
   <si>
     <t>Verpflichtende Angabe: working | snapshot | changes. https://hl7.org/fhir/R4/valueset-list-mode.html
-Der Medikationsplan ist ein laufend gepflegtes Dokument: working</t>
+Der Medikationsplan ist ein laufend gepflegtes Dokument: working.</t>
   </si>
   <si>
     <t>How this list was prepared - whether it is a working list that is suitable for being maintained on an ongoing basis, or if it represents a snapshot of a list of items from another source, or whether it is a prepared list where items may be marked as added, modified or deleted.</t>
@@ -522,6 +524,9 @@
   </si>
   <si>
     <t>Lists are used in various ways, and it must be known in what way it is safe to use them.</t>
+  </si>
+  <si>
+    <t>working</t>
   </si>
   <si>
     <t>The processing mode that applies to this list.</t>
@@ -705,7 +710,8 @@
     <t>List.orderedBy</t>
   </si>
   <si>
-    <t>Die Reihenfolge der Einträge im Medikationsplan ist fachlich relevant und wird durch den Ersteller vorgegeben. 
+    <t>Die Reihenfolge der Einträge im Medikationsplan ist fachlich relevant und wird durch den Ersteller vorgegeben. Da nicht verpflichtend, könnte das Element auch 0..0 gesetzt werden.
+Evtl. Unterscheidung user und patient.
 Mögliche Codes: user | system | event-date | entry-date| priority | alphabetic | category | patient (TODO: nur user oder andere Reihenfolge ermöglichen?)</t>
   </si>
   <si>
@@ -814,10 +820,16 @@
     <t>List.entry.flag</t>
   </si>
   <si>
-    <t>Kennzeichnet die Art der Änderung des Medikationsplaneintrags: zB Unchanged | Changed | Cancelled | Prescribed | Ceased | Suspended.</t>
-  </si>
-  <si>
-    <t>The flag allows the system constructing the list to indicate the role and significance of the item in the list.</t>
+    <t>Kennzeichnet die Art der Änderung des Medikationsplaneintrags: (example) Unchanged | Changed | Cancelled | Prescribed | Ceased | Suspended. Details siehe Definition.</t>
+  </si>
+  <si>
+    <t>Kennzeichnet die Art der Änderung des Medikationsplaneintrags: 
+* \"Unchanged\": Medikationsplaneintrag bleibt unverändert bestehen
+* \"Changed\": Medikationsplaneintrag wird geändert
+* \"Cancelled\": Medikationsplaneintrag wird storniert
+* \"Prescribed\": Neuer Medikationsplaneintrag wurde hinzugefügt
+* \"Ceased\": Medikationsplaneintrag wird abgesetzt
+* \"Suspended\": Medikationsplaneintrag wird pausiert</t>
   </si>
   <si>
     <t>The flag can only be understood in the context of the List.code. If the flag means that the entry has actually been deleted from the list, the deleted element SHALL be true. Deleted can only be used if the List.mode is "changes".</t>
@@ -892,13 +904,13 @@
     <t>List.emptyReason</t>
   </si>
   <si>
-    <t>Begründung, warum der Medikationsplan leer ist: 
-https://hl7.org/fhir/R4/valueset-list-empty-reason.html eingeschränkt auf: &lt;vbr&gt;
+    <t>Begründung, warum der Medikationsplan leer ist: notstarted |  nilknown. Details siehe Definition.</t>
+  </si>
+  <si>
+    <t>Begründung, warum der Medikationsplan leer ist. Eingeschränkt auf: &lt;vbr&gt;
     - notstarted: Intitalzustand &lt;br&gt;
-    - nilknown: Patient nimmt derzeit keine Medikamente ein</t>
-  </si>
-  <si>
-    <t>If the list is empty, why the list is empty.</t>
+    - nilknown: Patient nimmt derzeit keine Medikamente ein
+https://hl7.org/fhir/R4/valueset-list-empty-reason.html</t>
   </si>
   <si>
     <t>The various reasons for an empty list make a significant interpretation to its interpretation. Note that this code is for use when the entire list has been suppressed, and not for when individual items are omitted - implementers may consider using a text note or a flag on an entry in these cases.</t>
@@ -2627,7 +2639,7 @@
         <v>21</v>
       </c>
       <c r="S13" t="s" s="2">
-        <v>21</v>
+        <v>162</v>
       </c>
       <c r="T13" t="s" s="2">
         <v>21</v>
@@ -2645,10 +2657,10 @@
         <v>152</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>21</v>
@@ -2681,18 +2693,18 @@
         <v>97</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2715,17 +2727,17 @@
         <v>86</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>21</v>
@@ -2738,7 +2750,7 @@
         <v>21</v>
       </c>
       <c r="T14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="U14" t="s" s="2">
         <v>21</v>
@@ -2774,7 +2786,7 @@
         <v>21</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -2789,7 +2801,7 @@
         <v>97</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>21</v>
@@ -2797,10 +2809,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2823,19 +2835,19 @@
         <v>86</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>21</v>
@@ -2845,7 +2857,7 @@
         <v>21</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>21</v>
@@ -2860,13 +2872,13 @@
         <v>21</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>21</v>
@@ -2884,7 +2896,7 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -2899,18 +2911,18 @@
         <v>97</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2933,19 +2945,19 @@
         <v>86</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>21</v>
@@ -2994,7 +3006,7 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3009,18 +3021,18 @@
         <v>97</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3043,13 +3055,13 @@
         <v>21</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3100,7 +3112,7 @@
         <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3115,18 +3127,18 @@
         <v>97</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3149,19 +3161,19 @@
         <v>86</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>21</v>
@@ -3210,7 +3222,7 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -3225,22 +3237,22 @@
         <v>97</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3259,19 +3271,19 @@
         <v>86</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>21</v>
@@ -3320,7 +3332,7 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -3335,18 +3347,18 @@
         <v>97</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3369,19 +3381,19 @@
         <v>21</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>21</v>
@@ -3391,7 +3403,7 @@
         <v>21</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>21</v>
@@ -3410,7 +3422,7 @@
       </c>
       <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>21</v>
@@ -3428,7 +3440,7 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3443,7 +3455,7 @@
         <v>97</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>21</v>
@@ -3451,10 +3463,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3477,13 +3489,13 @@
         <v>21</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3534,7 +3546,7 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -3549,7 +3561,7 @@
         <v>97</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>21</v>
@@ -3557,10 +3569,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3583,16 +3595,16 @@
         <v>21</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3642,7 +3654,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -3651,13 +3663,13 @@
         <v>78</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>21</v>
@@ -3665,10 +3677,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3691,13 +3703,13 @@
         <v>21</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3748,7 +3760,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -3763,7 +3775,7 @@
         <v>21</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>21</v>
@@ -3771,10 +3783,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3803,7 +3815,7 @@
         <v>132</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N24" t="s" s="2">
         <v>134</v>
@@ -3856,7 +3868,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -3871,7 +3883,7 @@
         <v>136</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>21</v>
@@ -3879,14 +3891,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -3908,10 +3920,10 @@
         <v>131</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N25" t="s" s="2">
         <v>134</v>
@@ -3966,7 +3978,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -3989,10 +4001,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4015,19 +4027,19 @@
         <v>21</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>21</v>
@@ -4056,7 +4068,7 @@
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>21</v>
@@ -4074,7 +4086,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4089,7 +4101,7 @@
         <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>21</v>
@@ -4097,10 +4109,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4123,71 +4135,71 @@
         <v>21</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="P27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q27" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="R27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="L27" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="P27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q27" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="R27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>255</v>
-      </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
       </c>
@@ -4195,13 +4207,13 @@
         <v>85</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>21</v>
@@ -4209,10 +4221,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4235,17 +4247,17 @@
         <v>21</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>21</v>
@@ -4294,7 +4306,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -4309,7 +4321,7 @@
         <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>21</v>
@@ -4317,10 +4329,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4343,13 +4355,13 @@
         <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4400,7 +4412,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>85</v>
@@ -4415,7 +4427,7 @@
         <v>97</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>21</v>
@@ -4423,10 +4435,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4449,19 +4461,19 @@
         <v>21</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>21</v>
@@ -4490,7 +4502,7 @@
       </c>
       <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>21</v>
@@ -4508,7 +4520,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -4517,13 +4529,13 @@
         <v>85</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T15:12:36+00:00</t>
+    <t>2026-03-27T10:18:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T10:18:57+00:00</t>
+    <t>2026-03-30T07:39:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T07:39:16+00:00</t>
+    <t>2026-03-30T10:13:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T10:13:35+00:00</t>
+    <t>2026-04-01T13:59:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T13:59:59+00:00</t>
+    <t>2026-04-02T15:01:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T15:01:02+00:00</t>
+    <t>2026-04-07T09:06:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T09:06:22+00:00</t>
+    <t>2026-04-07T15:41:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T15:41:53+00:00</t>
+    <t>2026-04-07T16:09:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T16:09:01+00:00</t>
+    <t>2026-04-08T18:33:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T18:33:44+00:00</t>
+    <t>2026-04-09T06:40:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T06:40:16+00:00</t>
+    <t>2026-04-09T18:30:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T18:30:31+00:00</t>
+    <t>2026-04-10T11:48:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T11:48:51+00:00</t>
+    <t>2026-04-13T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -88,7 +88,7 @@
   </si>
   <si>
     <t>Bildet den Medikationsplan eines ELGA-Teilnehmers ab ("List"-Ressource). 
-Die Liste beinhaltet Referenzen auf 0..* Medikationsplaneinträge (MedicationRequests), die alle verordneten Arzneimittel und deren Dosierung abbilden.
+Die Liste beinhaltet Referenzen auf 0..* Medikationsplaneinträge (MedicationRequests), die alle geplanten Medikationen und deren Dosierung abbilden.
 Die Reihenfolge der Listenelemente kann duch den User festgelegt werden. Jedes Listenelement enthält einen Änderungsstatus.</t>
   </si>
   <si>
@@ -469,7 +469,7 @@
 </t>
   </si>
   <si>
-    <t>Logischer Identfier der Liste / des Medikationsplans. Verwendung zu prüfen.</t>
+    <t>Logischer Identfier der Liste (des Medikationsplans) zur Schreibintegritätsprüfung.</t>
   </si>
   <si>
     <t>Identifier for the List assigned for business purposes outside the context of FHIR.</t>
@@ -484,9 +484,7 @@
     <t>List.status</t>
   </si>
   <si>
-    <t>Verpflichtende Angabe: current | retired. https://hl7.org/fhir/R4/valueset-list-status.html
-TODO: retired nach Ableben des Patienten bis Ende der Aufbewahrungsfrist? automatisch gesetzt?
-entered-in-error nicht sinnvoll</t>
+    <t>Mögliche Ausprägungen: [current | retired] Bedeutung: current: default | retired: nach Ableben des Patienten bis Ende der Aufbewahrungsfrist</t>
   </si>
   <si>
     <t>Indicates the current state of this list.</t>
@@ -513,8 +511,7 @@
     <t>List.mode</t>
   </si>
   <si>
-    <t>Verpflichtende Angabe: working | snapshot | changes. https://hl7.org/fhir/R4/valueset-list-mode.html
-Der Medikationsplan ist ein laufend gepflegtes Dokument: working.</t>
+    <t>Der Medikationsplan ist ein laufend gepflegtes Dokument. Fixer Wert: working.</t>
   </si>
   <si>
     <t>How this list was prepared - whether it is a working list that is suitable for being maintained on an ongoing basis, or if it represents a snapshot of a list of items from another source, or whether it is a prepared list where items may be marked as added, modified or deleted.</t>
@@ -548,7 +545,7 @@
 </t>
   </si>
   <si>
-    <t>Titel der Liste. Verwendung zu prüfen.</t>
+    <t>Titel der Liste.</t>
   </si>
   <si>
     <t>A label for the list assigned by the author.</t>
@@ -570,7 +567,7 @@
 </t>
   </si>
   <si>
-    <t>Code, der den Typ der Liste beschreibt. https://hl7.org/fhir/R4/valueset-list-example-codes.html. Zu prüfen, ob/wie in Medikationsplan verwendet.</t>
+    <t>Code, der den Typ der Liste beschreibt.</t>
   </si>
   <si>
     <t>This code defines the purpose of the list - why it was created.</t>
@@ -586,7 +583,7 @@
   &lt;coding&gt;
     &lt;system value="http://snomed.info/sct"/&gt;
     &lt;code value="736378000"/&gt;
-    &lt;display value="Medication management plan (record artifact)"/&gt;
+    &lt;display value="Medikationsplan"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>
@@ -613,7 +610,7 @@
 </t>
   </si>
   <si>
-    <t>Patient, für den der Medikationsplan erstellt werden soll, der über den 
+    <t>Patient, für den der Medikationsplan dokumentiert wird, der über den 
 Zentralen Patientenindex identifizierbar und Teilnehmer von ELGA e-Medikation ist.</t>
   </si>
   <si>
@@ -639,7 +636,7 @@
 </t>
   </si>
   <si>
-    <t>Verwendung zu prüfen.</t>
+    <t>Behandlungskontext, in dem die Liste erstellt wurde.</t>
   </si>
   <si>
     <t>The encounter that is the context in which this list was created.</t>
@@ -687,7 +684,7 @@
 </t>
   </si>
   <si>
-    <t>Arzt oder Ärztin, die den Medikationsplans erstellt und für den Inhalt verantwortlich ist. 
+    <t>Arzt oder Ärztin, die den Medikationsplans erstellt hat und für den Inhalt verantwortlich ist. 
 Eindeutig identifiziert über den GDA-Index und berechtigt auf die ELGA e-Medikation 
 des Patienten zuzugreifen. Device nur für initiale Erstellung durch die Fachanwendung. Patient nur zur Änderung der Reihenfolge der Planeinträge oder nachdem er Einträge gelöscht hat.</t>
   </si>
@@ -820,16 +817,10 @@
     <t>List.entry.flag</t>
   </si>
   <si>
-    <t>Kennzeichnet die Art der Änderung des Medikationsplaneintrags: (example) Unchanged | Changed | Cancelled | Prescribed | Ceased | Suspended. Details siehe Definition.</t>
-  </si>
-  <si>
-    <t>Kennzeichnet die Art der Änderung des Medikationsplaneintrags: 
-* \"Unchanged\": Medikationsplaneintrag bleibt unverändert bestehen
-* \"Changed\": Medikationsplaneintrag wird geändert
-* \"Cancelled\": Medikationsplaneintrag wird storniert
-* \"Prescribed\": Neuer Medikationsplaneintrag wurde hinzugefügt
-* \"Ceased\": Medikationsplaneintrag wird abgesetzt
-* \"Suspended\": Medikationsplaneintrag wird pausiert</t>
+    <t>Kennzeichnet die Art der Änderung des Medikationsplaneintrags: [New | Unchanged | Changed | Removed] Bedeutung: New: Neuer Planeintrag wird hinzugefügt | Unchanged: Bestehender Planeintrag wird beibehalten und zur Kenntnis genommen | Changed: Bestehender Planeintrag wird geändert | Removed: Bestehender Planeintrag wird entfernt</t>
+  </si>
+  <si>
+    <t>The flag allows the system constructing the list to indicate the role and significance of the item in the list.</t>
   </si>
   <si>
     <t>The flag can only be understood in the context of the List.code. If the flag means that the entry has actually been deleted from the list, the deleted element SHALL be true. Deleted can only be used if the List.mode is "changes".</t>
@@ -838,7 +829,7 @@
     <t>This field is present to support various clinical uses of lists, such as a discharge summary medication list, where flags specify whether the medication was added, modified, or deleted from the list.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/list-item-flag</t>
+    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/ElgaListEntryFlagVS</t>
   </si>
   <si>
     <t>List.entry.deleted</t>
@@ -904,13 +895,10 @@
     <t>List.emptyReason</t>
   </si>
   <si>
-    <t>Begründung, warum der Medikationsplan leer ist: notstarted |  nilknown. Details siehe Definition.</t>
-  </si>
-  <si>
-    <t>Begründung, warum der Medikationsplan leer ist. Eingeschränkt auf: &lt;vbr&gt;
-    - notstarted: Intitalzustand &lt;br&gt;
-    - nilknown: Patient nimmt derzeit keine Medikamente ein
-https://hl7.org/fhir/R4/valueset-list-empty-reason.html</t>
+    <t>Begründung, warum der Medikationsplan leer ist. Mögliche Ausprägungen: [notstarted |  nilknown] Bedeutung: notstarted: Intitalzustand - noch nie befüllt | nilknown: Patient nimmt derzeit keine Medikamente ein</t>
+  </si>
+  <si>
+    <t>If the list is empty, why the list is empty.</t>
   </si>
   <si>
     <t>The various reasons for an empty list make a significant interpretation to its interpretation. Note that this code is for use when the entire list has been suppressed, and not for when individual items are omitted - implementers may consider using a text note or a flag on an entry in these cases.</t>
@@ -919,7 +907,7 @@
     <t>Allows capturing things like "none exist" or "not asked" which can be important for most lists.</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/MedikationsplanEmptyReasonVS</t>
+    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/ElgaListEmptyReasonVS</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ,code&lt;ListEmptyReason].value[type=CD]</t>
@@ -1275,7 +1263,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="36.34375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="59.109375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.390625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
@@ -2636,10 +2624,10 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>21</v>
+        <v>162</v>
       </c>
       <c r="S13" t="s" s="2">
-        <v>162</v>
+        <v>21</v>
       </c>
       <c r="T13" t="s" s="2">
         <v>21</v>
@@ -2854,10 +2842,10 @@
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" t="s" s="2">
-        <v>21</v>
+        <v>180</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>180</v>
+        <v>21</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>21</v>
@@ -4123,7 +4111,7 @@
         <v>77</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>86</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="281">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T14:44:53+00:00</t>
+    <t>2026-04-13T15:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -496,10 +496,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>The current state of the list.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/list-status|4.0.1</t>
+    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/ElgaListStatusVS</t>
   </si>
   <si>
     <t>.status[current=active;retired=obsolete;entered-in-error=nullified]</t>
@@ -2534,11 +2531,9 @@
       <c r="X12" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="Y12" t="s" s="2">
+      <c r="Y12" s="2"/>
+      <c r="Z12" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>21</v>
@@ -2571,18 +2566,18 @@
         <v>97</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AL12" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>156</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2608,23 +2603,23 @@
         <v>105</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="N13" t="s" s="2">
+      <c r="O13" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>161</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>21</v>
@@ -2645,11 +2640,11 @@
         <v>152</v>
       </c>
       <c r="Y13" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="Z13" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="Z13" t="s" s="2">
-        <v>164</v>
-      </c>
       <c r="AA13" t="s" s="2">
         <v>21</v>
       </c>
@@ -2666,7 +2661,7 @@
         <v>21</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>85</v>
@@ -2681,18 +2676,18 @@
         <v>97</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AL13" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>166</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2715,17 +2710,17 @@
         <v>86</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L14" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="M14" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>21</v>
@@ -2738,7 +2733,7 @@
         <v>21</v>
       </c>
       <c r="T14" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="U14" t="s" s="2">
         <v>21</v>
@@ -2774,7 +2769,7 @@
         <v>21</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -2789,7 +2784,7 @@
         <v>97</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>21</v>
@@ -2797,10 +2792,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2823,51 +2818,51 @@
         <v>86</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="N15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="S15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X15" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="S15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X15" t="s" s="2">
+      <c r="Y15" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="Y15" t="s" s="2">
+      <c r="Z15" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="Z15" t="s" s="2">
-        <v>183</v>
-      </c>
       <c r="AA15" t="s" s="2">
         <v>21</v>
       </c>
@@ -2884,7 +2879,7 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -2899,18 +2894,18 @@
         <v>97</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AL15" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>185</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2933,19 +2928,19 @@
         <v>86</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="N16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>21</v>
@@ -2994,7 +2989,7 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3009,18 +3004,18 @@
         <v>97</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AL16" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="AL16" t="s" s="2">
-        <v>193</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3043,13 +3038,13 @@
         <v>21</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3100,7 +3095,7 @@
         <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3115,18 +3110,18 @@
         <v>97</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AL17" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>199</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3149,19 +3144,19 @@
         <v>86</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>21</v>
@@ -3210,7 +3205,7 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -3225,22 +3220,22 @@
         <v>97</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AL18" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>207</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3259,19 +3254,19 @@
         <v>86</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="N19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>21</v>
@@ -3320,7 +3315,7 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -3335,18 +3330,18 @@
         <v>97</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AL19" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="AL19" t="s" s="2">
-        <v>216</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3369,19 +3364,19 @@
         <v>21</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="N20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>21</v>
@@ -3391,7 +3386,7 @@
         <v>21</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>21</v>
@@ -3410,7 +3405,7 @@
       </c>
       <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>21</v>
@@ -3428,7 +3423,7 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3443,7 +3438,7 @@
         <v>97</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>21</v>
@@ -3451,10 +3446,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3477,13 +3472,13 @@
         <v>21</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3534,7 +3529,7 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -3549,7 +3544,7 @@
         <v>97</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>21</v>
@@ -3557,10 +3552,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3583,16 +3578,16 @@
         <v>21</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3642,7 +3637,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -3651,13 +3646,13 @@
         <v>78</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>21</v>
@@ -3665,10 +3660,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3691,13 +3686,13 @@
         <v>21</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3748,22 +3743,22 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK23" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="AG23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH23" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI23" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ23" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AK23" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>21</v>
@@ -3771,10 +3766,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3803,7 +3798,7 @@
         <v>132</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="N24" t="s" s="2">
         <v>134</v>
@@ -3856,7 +3851,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -3871,7 +3866,7 @@
         <v>136</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>21</v>
@@ -3879,14 +3874,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -3908,10 +3903,10 @@
         <v>131</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="N25" t="s" s="2">
         <v>134</v>
@@ -3966,7 +3961,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -3989,10 +3984,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4015,19 +4010,19 @@
         <v>21</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>21</v>
@@ -4056,7 +4051,7 @@
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>21</v>
@@ -4074,7 +4069,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4089,7 +4084,7 @@
         <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>21</v>
@@ -4097,10 +4092,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4123,85 +4118,85 @@
         <v>21</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="O27" t="s" s="2">
+      <c r="P27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q27" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="P27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q27" t="s" s="2">
+      <c r="R27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF27" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI27" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="R27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="AG27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH27" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI27" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>21</v>
@@ -4209,10 +4204,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4235,17 +4230,17 @@
         <v>21</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>21</v>
@@ -4294,7 +4289,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -4309,7 +4304,7 @@
         <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>21</v>
@@ -4317,10 +4312,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4343,13 +4338,13 @@
         <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4400,7 +4395,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>85</v>
@@ -4415,7 +4410,7 @@
         <v>97</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>21</v>
@@ -4423,10 +4418,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4449,19 +4444,19 @@
         <v>21</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="N30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>21</v>
@@ -4490,7 +4485,7 @@
       </c>
       <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>21</v>
@@ -4508,7 +4503,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -4517,13 +4512,13 @@
         <v>85</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T15:27:52+00:00</t>
+    <t>2026-04-13T20:12:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,9 +87,9 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Bildet den Medikationsplan eines ELGA-Teilnehmers ab ("List"-Ressource). 
-Die Liste beinhaltet Referenzen auf 0..* Medikationsplaneinträge (MedicationRequests), die alle geplanten Medikationen und deren Dosierung abbilden.
-Die Reihenfolge der Listenelemente kann duch den User festgelegt werden. Jedes Listenelement enthält einen Änderungsstatus.</t>
+    <t>Der Medikationsplan eines ELGA-Teilnehmers bzw. einer ELGA-Teilnehmerin wird durch eine List-Ressource abgebildet. 
+Diese enthält 0..* Einträge (List.entry), wobei jedes Entry genau eine Referenz auf einen Medikationsplaneintrag (MedicationRequest) in List.entry.item beinhaltet.
+Die Reihenfolge der Einträge kann durch den GDA oder den Patienten festgelegt werden. Jeder Listeneintrag enthält im Element List.entry.flag den Änderungsstatus des jeweiligen Medikationsplaneintrags.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -469,7 +469,7 @@
 </t>
   </si>
   <si>
-    <t>Logischer Identfier der Liste (des Medikationsplans) zur Schreibintegritätsprüfung.</t>
+    <t>Logischer Identfier der Liste (des Medikationsplans) zur Integritätsprüfung beim Schreibvorgang.</t>
   </si>
   <si>
     <t>Identifier for the List assigned for business purposes outside the context of FHIR.</t>
@@ -704,9 +704,7 @@
     <t>List.orderedBy</t>
   </si>
   <si>
-    <t>Die Reihenfolge der Einträge im Medikationsplan ist fachlich relevant und wird durch den Ersteller vorgegeben. Da nicht verpflichtend, könnte das Element auch 0..0 gesetzt werden.
-Evtl. Unterscheidung user und patient.
-Mögliche Codes: user | system | event-date | entry-date| priority | alphabetic | category | patient (TODO: nur user oder andere Reihenfolge ermöglichen?)</t>
+    <t>Die Reihenfolge der Einträge im Medikationsplan ist fachlich relevant und wird durch den Ersteller vorgegeben.</t>
   </si>
   <si>
     <t>What order applies to the items in the list.</t>
@@ -738,7 +736,7 @@
 </t>
   </si>
   <si>
-    <t>Freitextliche Anmerkungen zum Medikationsplan. TODO: prüfen, ob fachlich sinnvoll.</t>
+    <t>Freitextliche Anmerkungen zum Medikationsplan.</t>
   </si>
   <si>
     <t>Comments that apply to the overall list.</t>
@@ -754,7 +752,7 @@
 </t>
   </si>
   <si>
-    <t>Entries in the list</t>
+    <t>Medikationsplaneinträge in der Liste</t>
   </si>
   <si>
     <t>Entries in this list.</t>
@@ -836,7 +834,8 @@
 </t>
   </si>
   <si>
-    <t>Gibt an, ob der referenzierte Medikationsplaneintrag zur Entfernung markiert wurde. Unklar, ob Löschen so abgebildet werden soll oder einfach der Eintrag nicht mehr enthalten ist.</t>
+    <t>Gibt an, ob der referenzierte Medikationsplaneintrag zur Entfernung markiert wurde.
+Keine Verwendung im Medikationsplan, da GDA für die Kennzeichnung von zur Entfernung freigegebenen Planeinträgen das Element entry.flag mit dem Wert "removed" verwenden und ELGA-Teilnehmer Einträge durch Entfernen aus der Liste löschen.</t>
   </si>
   <si>
     <t>True if this item is marked as deleted in the list.</t>
@@ -861,7 +860,7 @@
     <t>List.entry.date</t>
   </si>
   <si>
-    <t>Datum der Aufnahme / Änderung des Medikationsplaneintrags. Fachlich zu klären.</t>
+    <t>Datum der Aufnahme bzw. Änderung des Medikationsplaneintrags.</t>
   </si>
   <si>
     <t>When this item was added to the list.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T20:12:42+00:00</t>
+    <t>2026-04-14T10:13:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>85</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T10:13:14+00:00</t>
+    <t>2026-04-17T19:15:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T19:15:07+00:00</t>
+    <t>2026-04-20T08:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T08:20:06+00:00</t>
+    <t>2026-04-20T16:24:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T16:24:35+00:00</t>
+    <t>2026-04-20T19:04:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -484,7 +484,7 @@
     <t>List.status</t>
   </si>
   <si>
-    <t>Mögliche Ausprägungen: [current | retired] Bedeutung: current: default | retired: nach Ableben des Patienten bis Ende der Aufbewahrungsfrist</t>
+    <t>Status des Medikationsplans. Mögliche Ausprägungen: [current | retired] Bedeutung: current: default | retired: nach Ableben des Patienten bis Ende der Aufbewahrungsfrist</t>
   </si>
   <si>
     <t>Indicates the current state of this list.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T19:04:12+00:00</t>
+    <t>2026-04-21T08:44:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T08:44:51+00:00</t>
+    <t>2026-04-21T11:54:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T11:54:48+00:00</t>
+    <t>2026-04-21T14:09:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T14:09:10+00:00</t>
+    <t>2026-04-21T17:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T17:01:26+00:00</t>
+    <t>2026-04-22T08:49:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-22T08:49:17+00:00</t>
+    <t>2026-04-22T10:01:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-22T10:01:54+00:00</t>
+    <t>2026-04-22T10:11:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-22T10:11:27+00:00</t>
+    <t>2026-04-28T11:58:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="280">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-28T11:58:02+00:00</t>
+    <t>2026-04-29T14:27:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -89,7 +89,7 @@
   <si>
     <t>Der Medikationsplan eines ELGA-Teilnehmers bzw. einer ELGA-Teilnehmerin wird durch eine List-Ressource abgebildet. 
 Diese enthält 0..* Einträge (List.entry), wobei jedes Entry genau eine Referenz auf einen Medikationsplaneintrag (MedicationRequest) in List.entry.item beinhaltet.
-Die Reihenfolge der Einträge kann durch den GDA oder den Patienten festgelegt werden. Jeder Listeneintrag enthält im Element List.entry.flag den Änderungsstatus des jeweiligen Medikationsplaneintrags.</t>
+Die Reihenfolge der Einträge kann durch den GDA festgelegt werden. Jeder Listeneintrag enthält im Element List.entry.flag den Änderungsstatus des jeweiligen Medikationsplaneintrags.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -119,7 +119,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/List</t>
+    <t>https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-core-list</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -469,7 +469,7 @@
 </t>
   </si>
   <si>
-    <t>Logischer Identfier der Liste (des Medikationsplans) zur Integritätsprüfung beim Schreibvorgang.</t>
+    <t>Logischer Identfier der Liste zur Integritätsprüfung beim Schreibvorgang.</t>
   </si>
   <si>
     <t>Identifier for the List assigned for business purposes outside the context of FHIR.</t>
@@ -508,7 +508,7 @@
     <t>List.mode</t>
   </si>
   <si>
-    <t>Der Medikationsplan ist ein laufend gepflegtes Dokument. Fixer Wert: working.</t>
+    <t>Die Liste wird laufend gepflegt, hat daher den fixen Wert: working.</t>
   </si>
   <si>
     <t>How this list was prepared - whether it is a working list that is suitable for being maintained on an ongoing basis, or if it represents a snapshot of a list of items from another source, or whether it is a prepared list where items may be marked as added, modified or deleted.</t>
@@ -542,7 +542,7 @@
 </t>
   </si>
   <si>
-    <t>Titel der Liste.</t>
+    <t>Die Liste hat keinen Titel.</t>
   </si>
   <si>
     <t>A label for the list assigned by the author.</t>
@@ -576,15 +576,6 @@
     <t>Lists often contain subsets of resources rather than an exhaustive list.  The code identifies what type of subset is included.</t>
   </si>
   <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="http://snomed.info/sct"/&gt;
-    &lt;code value="736378000"/&gt;
-    &lt;display value="Medikationsplan"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
     <t>example</t>
   </si>
   <si>
@@ -607,8 +598,8 @@
 </t>
   </si>
   <si>
-    <t>Patient, für den der Medikationsplan dokumentiert wird, der über den 
-Zentralen Patientenindex identifizierbar und Teilnehmer von ELGA e-Medikation ist.</t>
+    <t>Patient, für den die Liste geführt wird, der über den 
+Zentralen Patientenindex identifizierbar und Teilnehmer der ELGA-Anwendung ist.</t>
   </si>
   <si>
     <t>The common subject (or patient) of the resources that are in the list if there is one.</t>
@@ -633,7 +624,7 @@
 </t>
   </si>
   <si>
-    <t>Behandlungskontext, in dem die Liste erstellt wurde.</t>
+    <t>Es wird kein Behandlungskontext dokumentiert.</t>
   </si>
   <si>
     <t>The encounter that is the context in which this list was created.</t>
@@ -652,7 +643,7 @@
 </t>
   </si>
   <si>
-    <t>Letzte Aktualisierung des Medikationsplans.</t>
+    <t>Letzte Aktualisierung der Liste.</t>
   </si>
   <si>
     <t>The date that the list was prepared.</t>
@@ -681,9 +672,9 @@
 </t>
   </si>
   <si>
-    <t>Arzt oder Ärztin, die den Medikationsplans erstellt hat und für den Inhalt verantwortlich ist. 
-Eindeutig identifiziert über den GDA-Index und berechtigt auf die ELGA e-Medikation 
-des Patienten zuzugreifen. Device nur für initiale Erstellung durch die Fachanwendung. Patient nur zur Änderung der Reihenfolge der Planeinträge oder nachdem er Einträge gelöscht hat.</t>
+    <t>Person, die die Liste erstellt hat und für den Inhalt verantwortlich ist. 
+Im Falle eines GDA: eindeutig identifiziert über den GDA-Index und berechtigt auf die ELGA-Anwendung 
+des Patienten zuzugreifen.</t>
   </si>
   <si>
     <t>The entity responsible for deciding what the contents of the list were. Where the list was created by a human, this is the same as the author of the list.</t>
@@ -704,7 +695,7 @@
     <t>List.orderedBy</t>
   </si>
   <si>
-    <t>Die Reihenfolge der Einträge im Medikationsplan ist fachlich relevant und wird durch den Ersteller vorgegeben.</t>
+    <t>Die Reihenfolge der Einträge wird über die List.entries durch den Ersteller vorgegeben.</t>
   </si>
   <si>
     <t>What order applies to the items in the list.</t>
@@ -716,14 +707,10 @@
     <t>Important for presentation and rendering.  Lists may be sorted to place more important information first or to group related entries.</t>
   </si>
   <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;code value="user"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/list-order</t>
+    <t>What order applies to the items in a list.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/list-order|4.0.1</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=COMP].sequenceNumber &gt; 1</t>
@@ -736,7 +723,7 @@
 </t>
   </si>
   <si>
-    <t>Freitextliche Anmerkungen zum Medikationsplan.</t>
+    <t>Keine Freitext-Anmerkungen auf Listenebene.</t>
   </si>
   <si>
     <t>Comments that apply to the overall list.</t>
@@ -752,7 +739,7 @@
 </t>
   </si>
   <si>
-    <t>Medikationsplaneinträge in der Liste</t>
+    <t>Die Reihenfolge der Einträge der Liste ist fachlich relevant und wird durch den Ersteller vorgegeben.</t>
   </si>
   <si>
     <t>Entries in this list.</t>
@@ -812,7 +799,7 @@
     <t>List.entry.flag</t>
   </si>
   <si>
-    <t>Kennzeichnet die Art der Änderung des Medikationsplaneintrags: [New | Unchanged | Changed | Removed] Bedeutung: New: Neuer Planeintrag wird hinzugefügt | Unchanged: Bestehender Planeintrag wird beibehalten und zur Kenntnis genommen | Changed: Bestehender Planeintrag wird geändert | Removed: Bestehender Planeintrag wird entfernt</t>
+    <t>Kennzeichnet die Art der Änderung des Listeneintrags: [New | Unchanged | Changed | Removed] Bedeutung: New: Neuer Eintrag wird hinzugefügt | Unchanged: Bestehender Eintrag wird beibehalten und zur Kenntnis genommen | Changed: Bestehender Eintrag wird geändert | Removed: Bestehender Eintrag wird entfernt</t>
   </si>
   <si>
     <t>The flag allows the system constructing the list to indicate the role and significance of the item in the list.</t>
@@ -834,8 +821,7 @@
 </t>
   </si>
   <si>
-    <t>Gibt an, ob der referenzierte Medikationsplaneintrag zur Entfernung markiert wurde.
-Keine Verwendung im Medikationsplan, da GDA für die Kennzeichnung von zur Entfernung freigegebenen Planeinträgen das Element entry.flag mit dem Wert "removed" verwenden und ELGA-Teilnehmer Einträge durch Entfernen aus der Liste löschen.</t>
+    <t>Kann nur verwendet werden, wenn list.mode = changes, daher keine Verwendung im Medikationsplan.</t>
   </si>
   <si>
     <t>True if this item is marked as deleted in the list.</t>
@@ -860,7 +846,7 @@
     <t>List.entry.date</t>
   </si>
   <si>
-    <t>Datum der Aufnahme bzw. Änderung des Medikationsplaneintrags.</t>
+    <t>Datum der Aufnahme bzw. Änderung des Eintrags ist im Eintrag (in der referenzierten Ressource) ersichtlich.</t>
   </si>
   <si>
     <t>When this item was added to the list.</t>
@@ -879,7 +865,7 @@
 </t>
   </si>
   <si>
-    <t>Referenz auf einen Medikationsplaneintrag.</t>
+    <t>Referenz auf einen Eintrag.</t>
   </si>
   <si>
     <t>A reference to the actual resource from which data was derived.</t>
@@ -891,7 +877,7 @@
     <t>List.emptyReason</t>
   </si>
   <si>
-    <t>Begründung, warum der Medikationsplan leer ist. Mögliche Ausprägungen: [notstarted |  nilknown] Bedeutung: notstarted: Intitalzustand - noch nie befüllt | nilknown: Patient nimmt derzeit keine Medikamente ein</t>
+    <t>Begründung, warum die Liste leer ist. Mögliche Ausprägungen: [notstarted |  nilknown] Bedeutung: notstarted: Intitalzustand - noch nie befüllt | nilknown: Die Liste wurde explizit geleert.</t>
   </si>
   <si>
     <t>If the list is empty, why the list is empty.</t>
@@ -2836,31 +2822,31 @@
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X15" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="S15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X15" t="s" s="2">
+      <c r="Y15" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="Y15" t="s" s="2">
+      <c r="Z15" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>21</v>
@@ -2893,18 +2879,18 @@
         <v>97</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AL15" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>184</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2927,19 +2913,19 @@
         <v>86</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="N16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>190</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>21</v>
@@ -2988,7 +2974,7 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3003,18 +2989,18 @@
         <v>97</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AL16" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="AL16" t="s" s="2">
-        <v>192</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3037,13 +3023,13 @@
         <v>21</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3094,7 +3080,7 @@
         <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3109,18 +3095,18 @@
         <v>97</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AL17" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>198</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3143,19 +3129,19 @@
         <v>86</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>21</v>
@@ -3204,7 +3190,7 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -3219,22 +3205,22 @@
         <v>97</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AL18" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>206</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3253,19 +3239,19 @@
         <v>86</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="N19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>21</v>
@@ -3314,7 +3300,7 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -3329,18 +3315,18 @@
         <v>97</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AL19" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AL19" t="s" s="2">
-        <v>215</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3348,10 +3334,10 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>86</v>
@@ -3366,16 +3352,16 @@
         <v>174</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="N20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>21</v>
@@ -3385,27 +3371,29 @@
         <v>21</v>
       </c>
       <c r="S20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="Z20" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="T20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X20" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="Y20" s="2"/>
-      <c r="Z20" t="s" s="2">
-        <v>222</v>
-      </c>
       <c r="AA20" t="s" s="2">
         <v>21</v>
       </c>
@@ -3422,7 +3410,7 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3437,18 +3425,18 @@
         <v>97</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" hidden="true">
+      <c r="A21" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="AL20" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="2">
-        <v>224</v>
-      </c>
       <c r="B21" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3459,10 +3447,10 @@
         <v>77</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>21</v>
@@ -3471,13 +3459,13 @@
         <v>21</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3528,7 +3516,7 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -3543,7 +3531,7 @@
         <v>97</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>21</v>
@@ -3551,10 +3539,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3577,16 +3565,16 @@
         <v>21</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3636,7 +3624,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -3645,13 +3633,13 @@
         <v>78</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>21</v>
@@ -3659,10 +3647,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3688,10 +3676,10 @@
         <v>167</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3742,22 +3730,22 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK23" t="s" s="2">
         <v>239</v>
-      </c>
-      <c r="AG23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH23" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI23" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ23" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AK23" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>21</v>
@@ -3765,10 +3753,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3797,7 +3785,7 @@
         <v>132</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="N24" t="s" s="2">
         <v>134</v>
@@ -3850,7 +3838,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -3865,7 +3853,7 @@
         <v>136</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>21</v>
@@ -3873,14 +3861,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -3902,10 +3890,10 @@
         <v>131</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="N25" t="s" s="2">
         <v>134</v>
@@ -3960,7 +3948,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -3983,10 +3971,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4012,16 +4000,16 @@
         <v>174</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>21</v>
@@ -4050,7 +4038,7 @@
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>21</v>
@@ -4068,7 +4056,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4089,12 +4077,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4108,7 +4096,7 @@
         <v>77</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>86</v>
@@ -4117,85 +4105,85 @@
         <v>21</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="O27" t="s" s="2">
+      <c r="P27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q27" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="P27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q27" t="s" s="2">
+      <c r="R27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF27" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI27" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="R27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="AG27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH27" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI27" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>21</v>
@@ -4203,10 +4191,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4217,7 +4205,7 @@
         <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>86</v>
@@ -4229,17 +4217,17 @@
         <v>21</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>21</v>
@@ -4288,7 +4276,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -4303,7 +4291,7 @@
         <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>21</v>
@@ -4311,10 +4299,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4337,13 +4325,13 @@
         <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4394,7 +4382,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>85</v>
@@ -4409,7 +4397,7 @@
         <v>97</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>21</v>
@@ -4417,10 +4405,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4446,16 +4434,16 @@
         <v>174</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="N30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>21</v>
@@ -4484,7 +4472,7 @@
       </c>
       <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>21</v>
@@ -4502,7 +4490,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -4511,13 +4499,13 @@
         <v>85</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T14:27:58+00:00</t>
+    <t>2026-04-30T15:16:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -119,7 +119,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-core-list</t>
+    <t>https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-list</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -484,7 +484,7 @@
     <t>List.status</t>
   </si>
   <si>
-    <t>Status des Medikationsplans. Mögliche Ausprägungen: [current | retired] Bedeutung: current: default | retired: nach Ableben des Patienten bis Ende der Aufbewahrungsfrist</t>
+    <t>Status der Liste. Mögliche Ausprägungen: [current | retired] Bedeutung: current: default | retired: nach Ableben des Patienten bis Ende der Aufbewahrungsfrist</t>
   </si>
   <si>
     <t>Indicates the current state of this list.</t>
@@ -496,7 +496,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/ElgaListStatusVS</t>
+    <t>https://fhir.hl7.at/elga/core/r4/ValueSet/ElgaListStatusVS</t>
   </si>
   <si>
     <t>.status[current=active;retired=obsolete;entered-in-error=nullified]</t>
@@ -594,7 +594,7 @@
     <t>List.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-patient)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-patient)
 </t>
   </si>
   <si>
@@ -643,7 +643,7 @@
 </t>
   </si>
   <si>
-    <t>Letzte Aktualisierung der Liste.</t>
+    <t>Datum der letzten Aktualisierung der Liste.</t>
   </si>
   <si>
     <t>The date that the list was prepared.</t>
@@ -668,13 +668,13 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitionerRole|Device|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-patient)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitioner|https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitionerRole|Device|https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-patient)
 </t>
   </si>
   <si>
     <t>Person, die die Liste erstellt hat und für den Inhalt verantwortlich ist. 
 Im Falle eines GDA: eindeutig identifiziert über den GDA-Index und berechtigt auf die ELGA-Anwendung 
-des Patienten zuzugreifen.</t>
+des Patienten zuzugreifen. Im Falle eines Patienten: eindeutig identifiziert durch den ZPI.</t>
   </si>
   <si>
     <t>The entity responsible for deciding what the contents of the list were. Where the list was created by a human, this is the same as the author of the list.</t>
@@ -739,7 +739,7 @@
 </t>
   </si>
   <si>
-    <t>Die Reihenfolge der Einträge der Liste ist fachlich relevant und wird durch den Ersteller vorgegeben.</t>
+    <t>Die Reihenfolge der Listeneinträge ist fachlich relevant und wird durch den Ersteller durch die Reihung der Eintries festgelegt.</t>
   </si>
   <si>
     <t>Entries in this list.</t>
@@ -811,7 +811,7 @@
     <t>This field is present to support various clinical uses of lists, such as a discharge summary medication list, where flags specify whether the medication was added, modified, or deleted from the list.</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/ElgaListEntryFlagVS</t>
+    <t>https://fhir.hl7.at/elga/core/r4/ValueSet/ElgaListEntryFlagVS</t>
   </si>
   <si>
     <t>List.entry.deleted</t>
@@ -821,7 +821,7 @@
 </t>
   </si>
   <si>
-    <t>Kann nur verwendet werden, wenn list.mode = changes, daher keine Verwendung im Medikationsplan.</t>
+    <t>Keine Verwendung in der ELGA Core List (da list.mode immer working).</t>
   </si>
   <si>
     <t>True if this item is marked as deleted in the list.</t>
@@ -846,7 +846,7 @@
     <t>List.entry.date</t>
   </si>
   <si>
-    <t>Datum der Aufnahme bzw. Änderung des Eintrags ist im Eintrag (in der referenzierten Ressource) ersichtlich.</t>
+    <t>Kein Datum der Aufnahme bzw. Änderung des Eintrags im List.entry. Das Datum ist nur im in der referenzierten Ressource ersichtlich.</t>
   </si>
   <si>
     <t>When this item was added to the list.</t>
@@ -861,7 +861,7 @@
     <t>List.entry.item</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-mr-planeintrag)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -889,7 +889,7 @@
     <t>Allows capturing things like "none exist" or "not asked" which can be important for most lists.</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/ElgaListEmptyReasonVS</t>
+    <t>https://fhir.hl7.at/elga/core/r4/ValueSet/ElgaListEmptyReasonVS</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ,code&lt;ListEmptyReason].value[type=CD]</t>
@@ -1230,7 +1230,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="207.19921875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="192.703125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1245,7 +1245,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="36.34375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="52.390625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="51.3671875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
@@ -3321,7 +3321,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
         <v>215</v>
       </c>
@@ -3340,7 +3340,7 @@
         <v>77</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>21</v>
@@ -4189,7 +4189,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
         <v>263</v>
       </c>
@@ -4208,7 +4208,7 @@
         <v>77</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T15:16:21+00:00</t>
+    <t>2026-04-30T15:23:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="281">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T15:23:35+00:00</t>
+    <t>2026-05-04T14:46:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -576,6 +576,15 @@
     <t>Lists often contain subsets of resources rather than an exhaustive list.  The code identifies what type of subset is included.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://snomed.info/sct"/&gt;
+    &lt;code value="736378000"/&gt;
+    &lt;display value="Medikationsplan"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>example</t>
   </si>
   <si>
@@ -861,11 +870,11 @@
     <t>List.entry.item</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-mr-planeintrag)
 </t>
   </si>
   <si>
-    <t>Referenz auf einen Eintrag.</t>
+    <t>Referenz auf einen Medikationsplaneintrag.</t>
   </si>
   <si>
     <t>A reference to the actual resource from which data was derived.</t>
@@ -2822,7 +2831,7 @@
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" t="s" s="2">
-        <v>21</v>
+        <v>179</v>
       </c>
       <c r="S15" t="s" s="2">
         <v>21</v>
@@ -2840,13 +2849,13 @@
         <v>21</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>21</v>
@@ -2879,18 +2888,18 @@
         <v>97</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2913,19 +2922,19 @@
         <v>86</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>21</v>
@@ -2974,7 +2983,7 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -2989,18 +2998,18 @@
         <v>97</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3023,13 +3032,13 @@
         <v>21</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3080,7 +3089,7 @@
         <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3095,18 +3104,18 @@
         <v>97</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3129,19 +3138,19 @@
         <v>86</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>21</v>
@@ -3190,7 +3199,7 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -3205,22 +3214,22 @@
         <v>97</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3239,19 +3248,19 @@
         <v>86</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>21</v>
@@ -3300,7 +3309,7 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -3315,18 +3324,18 @@
         <v>97</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3352,16 +3361,16 @@
         <v>174</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>21</v>
@@ -3389,10 +3398,10 @@
         <v>109</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>21</v>
@@ -3410,7 +3419,7 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3425,7 +3434,7 @@
         <v>97</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>21</v>
@@ -3433,10 +3442,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3459,13 +3468,13 @@
         <v>21</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3516,7 +3525,7 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -3531,7 +3540,7 @@
         <v>97</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>21</v>
@@ -3539,10 +3548,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3565,16 +3574,16 @@
         <v>21</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3624,7 +3633,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -3633,13 +3642,13 @@
         <v>78</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>21</v>
@@ -3647,10 +3656,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3676,10 +3685,10 @@
         <v>167</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3730,7 +3739,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -3745,7 +3754,7 @@
         <v>21</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>21</v>
@@ -3753,10 +3762,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3785,7 +3794,7 @@
         <v>132</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N24" t="s" s="2">
         <v>134</v>
@@ -3838,7 +3847,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -3853,7 +3862,7 @@
         <v>136</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>21</v>
@@ -3861,14 +3870,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -3890,10 +3899,10 @@
         <v>131</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N25" t="s" s="2">
         <v>134</v>
@@ -3948,7 +3957,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -3971,10 +3980,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4000,16 +4009,16 @@
         <v>174</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>21</v>
@@ -4038,7 +4047,7 @@
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>21</v>
@@ -4056,7 +4065,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4079,10 +4088,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4105,71 +4114,71 @@
         <v>21</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="P27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q27" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="R27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="L27" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="P27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q27" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="R27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>254</v>
-      </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
       </c>
@@ -4177,13 +4186,13 @@
         <v>85</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>21</v>
@@ -4191,10 +4200,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4217,17 +4226,17 @@
         <v>21</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>21</v>
@@ -4276,7 +4285,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -4291,7 +4300,7 @@
         <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>21</v>
@@ -4299,10 +4308,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4325,13 +4334,13 @@
         <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4382,7 +4391,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>85</v>
@@ -4397,7 +4406,7 @@
         <v>97</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>21</v>
@@ -4405,10 +4414,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4434,16 +4443,16 @@
         <v>174</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>21</v>
@@ -4472,7 +4481,7 @@
       </c>
       <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>21</v>
@@ -4490,7 +4499,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -4499,13 +4508,13 @@
         <v>85</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-list-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T14:46:25+00:00</t>
+    <t>2026-05-08T13:20:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
